--- a/data/template/西门子报价与公式汇总数据.xlsx
+++ b/data/template/西门子报价与公式汇总数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-joii\project\CPQ-superpowers-v2\dev\data\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A783646-F811-4210-9CAE-227B8AB1D8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE7515B-04CF-4265-A5DE-AC20BBFF092B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公式汇总" sheetId="24" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3924" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4413" uniqueCount="341">
   <si>
     <t>客户名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1516,6 +1516,34 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>kg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -22729,7 +22757,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K211"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K212"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -22779,13 +22808,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>3110140157</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C2" s="4" t="s">
-        <v>218</v>
+        <v>155</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
@@ -22794,9 +22825,15 @@
         <v>219</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J2" s="4">
         <v>1.35E-2</v>
       </c>
@@ -22804,11 +22841,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120010019</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>220</v>
       </c>
@@ -22819,9 +22858,15 @@
         <v>219</v>
       </c>
       <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J3" s="4">
         <v>5.9420000000000001E-2</v>
       </c>
@@ -22829,11 +22874,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3120011179</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C4" s="4" t="s">
         <v>220</v>
       </c>
@@ -22844,9 +22891,15 @@
         <v>219</v>
       </c>
       <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J4" s="4">
         <v>9.8400000000000001E-2</v>
       </c>
@@ -22854,11 +22907,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>3120011180</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C5" s="4" t="s">
         <v>220</v>
       </c>
@@ -22869,9 +22924,15 @@
         <v>219</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="G5" s="4">
+        <v>4</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J5" s="4">
         <v>6.6400000000000001E-2</v>
       </c>
@@ -22879,11 +22940,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>3120011622</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C6" s="4" t="s">
         <v>220</v>
       </c>
@@ -22894,9 +22957,15 @@
         <v>219</v>
       </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J6" s="4">
         <v>7.3800000000000004E-2</v>
       </c>
@@ -22904,11 +22973,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3120011785</v>
       </c>
-      <c r="B7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C7" s="4" t="s">
         <v>220</v>
       </c>
@@ -22919,9 +22990,15 @@
         <v>219</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="G7" s="4">
+        <v>6</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J7" s="4">
         <v>5.9420000000000001E-2</v>
       </c>
@@ -22929,11 +23006,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>3120012121</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C8" s="4" t="s">
         <v>220</v>
       </c>
@@ -22944,9 +23023,15 @@
         <v>219</v>
       </c>
       <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="G8" s="4">
+        <v>7</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.24</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J8" s="4">
         <v>0.25800000000000001</v>
       </c>
@@ -22954,11 +23039,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3120012245</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C9" s="4" t="s">
         <v>220</v>
       </c>
@@ -22969,9 +23056,15 @@
         <v>219</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="G9" s="4">
+        <v>8</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J9" s="4">
         <v>2.6263999999999998</v>
       </c>
@@ -22979,11 +23072,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>3120012245</v>
       </c>
-      <c r="B10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C10" s="4" t="s">
         <v>220</v>
       </c>
@@ -22994,9 +23089,15 @@
         <v>165</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="G10" s="4">
+        <v>9</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J10" s="4">
         <v>0.37402030260000002</v>
       </c>
@@ -23004,11 +23105,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>3120012438</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C11" s="4" t="s">
         <v>220</v>
       </c>
@@ -23019,9 +23122,15 @@
         <v>219</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="4">
+        <v>10</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.27</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J11" s="4">
         <v>2.8812000000000002</v>
       </c>
@@ -23029,11 +23138,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>3120012438</v>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C12" s="4" t="s">
         <v>220</v>
       </c>
@@ -23044,9 +23155,15 @@
         <v>222</v>
       </c>
       <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J12" s="4">
         <v>0.41022132480000018</v>
       </c>
@@ -23054,11 +23171,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>3120012442</v>
       </c>
-      <c r="B13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C13" s="4" t="s">
         <v>220</v>
       </c>
@@ -23069,9 +23188,15 @@
         <v>219</v>
       </c>
       <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="G13" s="4">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J13" s="4">
         <v>1.03684</v>
       </c>
@@ -23079,11 +23204,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>3120012442</v>
       </c>
-      <c r="B14" s="4"/>
+      <c r="B14" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C14" s="4" t="s">
         <v>220</v>
       </c>
@@ -23094,9 +23221,15 @@
         <v>222</v>
       </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="G14" s="4">
+        <v>3</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J14" s="4">
         <v>0.14299999999999999</v>
       </c>
@@ -23104,11 +23237,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>3120012443</v>
       </c>
-      <c r="B15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C15" s="4" t="s">
         <v>220</v>
       </c>
@@ -23119,9 +23254,15 @@
         <v>219</v>
       </c>
       <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.31</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J15" s="4">
         <v>2.07368</v>
       </c>
@@ -23129,11 +23270,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>3120012443</v>
       </c>
-      <c r="B16" s="4"/>
+      <c r="B16" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C16" s="4" t="s">
         <v>220</v>
       </c>
@@ -23144,9 +23287,15 @@
         <v>222</v>
       </c>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="G16" s="4">
+        <v>5</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.32</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J16" s="4">
         <v>0.28599999999999998</v>
       </c>
@@ -23154,11 +23303,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>3120012444</v>
       </c>
-      <c r="B17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C17" s="4" t="s">
         <v>220</v>
       </c>
@@ -23169,9 +23320,15 @@
         <v>219</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="G17" s="4">
+        <v>6</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.33</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J17" s="4">
         <v>1.6130800000000001</v>
       </c>
@@ -23179,11 +23336,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>3120012444</v>
       </c>
-      <c r="B18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C18" s="4" t="s">
         <v>220</v>
       </c>
@@ -23194,9 +23353,15 @@
         <v>222</v>
       </c>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
+      <c r="G18" s="4">
+        <v>7</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.34</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J18" s="4">
         <v>0.222</v>
       </c>
@@ -23204,11 +23369,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>3120012445</v>
       </c>
-      <c r="B19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C19" s="4" t="s">
         <v>220</v>
       </c>
@@ -23219,9 +23386,15 @@
         <v>219</v>
       </c>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
+      <c r="G19" s="4">
+        <v>8</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J19" s="4">
         <v>0.80653999999999992</v>
       </c>
@@ -23229,11 +23402,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>3120012445</v>
       </c>
-      <c r="B20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C20" s="4" t="s">
         <v>220</v>
       </c>
@@ -23244,9 +23419,15 @@
         <v>222</v>
       </c>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="G20" s="4">
+        <v>9</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.36</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J20" s="4">
         <v>0.111</v>
       </c>
@@ -23254,11 +23435,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>3120012446</v>
       </c>
-      <c r="B21" s="4"/>
+      <c r="B21" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C21" s="4" t="s">
         <v>220</v>
       </c>
@@ -23269,9 +23452,15 @@
         <v>219</v>
       </c>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="G21" s="4">
+        <v>10</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J21" s="4">
         <v>0.70265999999999995</v>
       </c>
@@ -23279,11 +23468,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>3120012446</v>
       </c>
-      <c r="B22" s="4"/>
+      <c r="B22" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C22" s="4" t="s">
         <v>220</v>
       </c>
@@ -23294,9 +23485,15 @@
         <v>222</v>
       </c>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J22" s="4">
         <v>9.7900000000000001E-2</v>
       </c>
@@ -23304,11 +23501,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>3120012447</v>
       </c>
-      <c r="B23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C23" s="4" t="s">
         <v>220</v>
       </c>
@@ -23319,9 +23518,15 @@
         <v>219</v>
       </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="G23" s="4">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J23" s="4">
         <v>1.4053199999999999</v>
       </c>
@@ -23329,11 +23534,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>3120012447</v>
       </c>
-      <c r="B24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C24" s="4" t="s">
         <v>220</v>
       </c>
@@ -23344,9 +23551,15 @@
         <v>222</v>
       </c>
       <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="G24" s="4">
+        <v>3</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J24" s="4">
         <v>0.1958</v>
       </c>
@@ -23354,11 +23567,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>3120012460</v>
       </c>
-      <c r="B25" s="4"/>
+      <c r="B25" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C25" s="4" t="s">
         <v>218</v>
       </c>
@@ -23369,9 +23584,15 @@
         <v>219</v>
       </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
+      <c r="G25" s="4">
+        <v>4</v>
+      </c>
+      <c r="H25" s="4">
+        <v>1.9E-2</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J25" s="4">
         <v>5.7624000000000004</v>
       </c>
@@ -23379,11 +23600,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>3120012460</v>
       </c>
-      <c r="B26" s="4"/>
+      <c r="B26" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C26" s="4" t="s">
         <v>220</v>
       </c>
@@ -23394,9 +23617,15 @@
         <v>222</v>
       </c>
       <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+      <c r="G26" s="4">
+        <v>5</v>
+      </c>
+      <c r="H26" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J26" s="4">
         <v>0.82044264960000035</v>
       </c>
@@ -23404,11 +23633,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>3120012462</v>
       </c>
-      <c r="B27" s="4"/>
+      <c r="B27" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C27" s="4" t="s">
         <v>218</v>
       </c>
@@ -23420,10 +23651,14 @@
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
-        <v>2</v>
-      </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="H27" s="4">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J27" s="4">
         <v>3.395218491280001</v>
       </c>
@@ -23431,11 +23666,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>3120012462</v>
       </c>
-      <c r="B28" s="4"/>
+      <c r="B28" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C28" s="4" t="s">
         <v>220</v>
       </c>
@@ -23446,9 +23683,15 @@
         <v>222</v>
       </c>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+      <c r="G28" s="4">
+        <v>7</v>
+      </c>
+      <c r="H28" s="4">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J28" s="4">
         <v>7.3008849557522126E-2</v>
       </c>
@@ -23456,11 +23699,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>3120012491</v>
       </c>
-      <c r="B29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C29" s="4" t="s">
         <v>220</v>
       </c>
@@ -23471,9 +23716,15 @@
         <v>219</v>
       </c>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
+      <c r="G29" s="4">
+        <v>8</v>
+      </c>
+      <c r="H29" s="4">
+        <v>2.3E-2</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J29" s="4">
         <v>0.51600000000000001</v>
       </c>
@@ -23481,11 +23732,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>3120012530</v>
       </c>
-      <c r="B30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C30" s="4" t="s">
         <v>220</v>
       </c>
@@ -23497,10 +23750,14 @@
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4">
-        <v>2</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="H30" s="4">
+        <v>2.4E-2</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J30" s="4">
         <v>5.9717584836000004</v>
       </c>
@@ -23508,11 +23765,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>3120012530</v>
       </c>
-      <c r="B31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C31" s="4" t="s">
         <v>220</v>
       </c>
@@ -23523,9 +23782,15 @@
         <v>222</v>
       </c>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
+      <c r="G31" s="4">
+        <v>10</v>
+      </c>
+      <c r="H31" s="4">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J31" s="4">
         <v>0.12849557522123889</v>
       </c>
@@ -23533,11 +23798,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>3120012572</v>
       </c>
-      <c r="B32" s="4"/>
+      <c r="B32" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C32" s="4" t="s">
         <v>220</v>
       </c>
@@ -23548,9 +23815,15 @@
         <v>219</v>
       </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J32" s="4">
         <v>4.5227000000000004</v>
       </c>
@@ -23558,11 +23831,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>3120012572</v>
       </c>
-      <c r="B33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C33" s="4" t="s">
         <v>220</v>
       </c>
@@ -23573,9 +23848,15 @@
         <v>222</v>
       </c>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
+      <c r="G33" s="4">
+        <v>2</v>
+      </c>
+      <c r="H33" s="4">
+        <v>2.7E-2</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J33" s="4">
         <v>0.64400978880000004</v>
       </c>
@@ -23583,11 +23864,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>3120012573</v>
       </c>
-      <c r="B34" s="4"/>
+      <c r="B34" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C34" s="4" t="s">
         <v>220</v>
       </c>
@@ -23598,9 +23881,15 @@
         <v>58</v>
       </c>
       <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
+      <c r="G34" s="4">
+        <v>3</v>
+      </c>
+      <c r="H34" s="4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J34" s="4">
         <v>13.132</v>
       </c>
@@ -23608,11 +23897,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>3120012573</v>
       </c>
-      <c r="B35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C35" s="4" t="s">
         <v>220</v>
       </c>
@@ -23623,9 +23914,15 @@
         <v>222</v>
       </c>
       <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
+      <c r="G35" s="4">
+        <v>4</v>
+      </c>
+      <c r="H35" s="4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J35" s="4">
         <v>1.8697423103999991</v>
       </c>
@@ -23633,11 +23930,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>3120012574</v>
       </c>
-      <c r="B36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C36" s="4" t="s">
         <v>220</v>
       </c>
@@ -23648,9 +23947,15 @@
         <v>219</v>
       </c>
       <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="G36" s="4">
+        <v>5</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J36" s="4">
         <v>9.0454000000000008</v>
       </c>
@@ -23658,11 +23963,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>3120012574</v>
       </c>
-      <c r="B37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C37" s="4" t="s">
         <v>220</v>
       </c>
@@ -23673,9 +23980,15 @@
         <v>222</v>
       </c>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
+      <c r="G37" s="4">
+        <v>6</v>
+      </c>
+      <c r="H37" s="4">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J37" s="4">
         <v>1.2880195776000001</v>
       </c>
@@ -23683,11 +23996,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>3120013869</v>
       </c>
-      <c r="B38" s="4"/>
+      <c r="B38" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C38" s="4" t="s">
         <v>220</v>
       </c>
@@ -23698,9 +24013,15 @@
         <v>219</v>
       </c>
       <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
+      <c r="G38" s="4">
+        <v>7</v>
+      </c>
+      <c r="H38" s="4">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J38" s="4">
         <v>1.3131999999999999</v>
       </c>
@@ -23708,11 +24029,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>3120013869</v>
       </c>
-      <c r="B39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C39" s="4" t="s">
         <v>220</v>
       </c>
@@ -23723,9 +24046,15 @@
         <v>222</v>
       </c>
       <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
+      <c r="G39" s="4">
+        <v>8</v>
+      </c>
+      <c r="H39" s="4">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J39" s="4">
         <v>0.18701015130000001</v>
       </c>
@@ -23733,11 +24062,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>3120013875</v>
       </c>
-      <c r="B40" s="4"/>
+      <c r="B40" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C40" s="4" t="s">
         <v>220</v>
       </c>
@@ -23749,10 +24080,14 @@
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4">
-        <v>2</v>
-      </c>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="H40" s="4">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J40" s="4">
         <v>1.69760924564</v>
       </c>
@@ -23760,11 +24095,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>3120013875</v>
       </c>
-      <c r="B41" s="4"/>
+      <c r="B41" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C41" s="4" t="s">
         <v>220</v>
       </c>
@@ -23775,9 +24112,15 @@
         <v>222</v>
       </c>
       <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
+      <c r="G41" s="4">
+        <v>10</v>
+      </c>
+      <c r="H41" s="4">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J41" s="4">
         <v>3.6504424778761063E-2</v>
       </c>
@@ -23785,11 +24128,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>3120013879</v>
       </c>
-      <c r="B42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C42" s="4" t="s">
         <v>220</v>
       </c>
@@ -23801,10 +24146,14 @@
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4">
-        <v>2</v>
-      </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H42" s="4">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J42" s="4">
         <v>2.9858792418000002</v>
       </c>
@@ -23812,11 +24161,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>3120013879</v>
       </c>
-      <c r="B43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C43" s="4" t="s">
         <v>220</v>
       </c>
@@ -23827,9 +24178,15 @@
         <v>222</v>
       </c>
       <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
+      <c r="G43" s="4">
+        <v>2</v>
+      </c>
+      <c r="H43" s="4">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J43" s="4">
         <v>6.4247787610619472E-2</v>
       </c>
@@ -23837,11 +24194,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>3120013885</v>
       </c>
-      <c r="B44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C44" s="4" t="s">
         <v>220</v>
       </c>
@@ -23852,9 +24211,15 @@
         <v>219</v>
       </c>
       <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
+      <c r="G44" s="4">
+        <v>3</v>
+      </c>
+      <c r="H44" s="4">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J44" s="4">
         <v>6.5659999999999998</v>
       </c>
@@ -23862,11 +24227,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>3120013885</v>
       </c>
-      <c r="B45" s="4"/>
+      <c r="B45" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C45" s="4" t="s">
         <v>220</v>
       </c>
@@ -23877,9 +24244,15 @@
         <v>222</v>
       </c>
       <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
+      <c r="G45" s="4">
+        <v>4</v>
+      </c>
+      <c r="H45" s="4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J45" s="4">
         <v>0.93487115519999975</v>
       </c>
@@ -23887,11 +24260,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>3120014677</v>
       </c>
-      <c r="B46" s="4"/>
+      <c r="B46" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C46" s="4" t="s">
         <v>220</v>
       </c>
@@ -23902,9 +24277,15 @@
         <v>219</v>
       </c>
       <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
+      <c r="G46" s="4">
+        <v>5</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J46" s="4">
         <v>2.3800000000000002E-2</v>
       </c>
@@ -23912,11 +24293,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>3120014678</v>
       </c>
-      <c r="B47" s="4"/>
+      <c r="B47" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C47" s="4" t="s">
         <v>220</v>
       </c>
@@ -23927,9 +24310,15 @@
         <v>219</v>
       </c>
       <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
+      <c r="G47" s="4">
+        <v>6</v>
+      </c>
+      <c r="H47" s="4">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J47" s="4">
         <v>2.3800000000000002E-2</v>
       </c>
@@ -23937,11 +24326,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>3120014679</v>
       </c>
-      <c r="B48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C48" s="4" t="s">
         <v>220</v>
       </c>
@@ -23952,9 +24343,15 @@
         <v>219</v>
       </c>
       <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
+      <c r="G48" s="4">
+        <v>7</v>
+      </c>
+      <c r="H48" s="4">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J48" s="4">
         <v>4.9399999999999999E-2</v>
       </c>
@@ -23962,11 +24359,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>3120014680</v>
       </c>
-      <c r="B49" s="4"/>
+      <c r="B49" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C49" s="4" t="s">
         <v>218</v>
       </c>
@@ -23977,9 +24376,15 @@
         <v>219</v>
       </c>
       <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
+      <c r="G49" s="4">
+        <v>8</v>
+      </c>
+      <c r="H49" s="4">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J49" s="4">
         <v>3.705E-2</v>
       </c>
@@ -23987,11 +24392,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>3120014682</v>
       </c>
-      <c r="B50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C50" s="4" t="s">
         <v>220</v>
       </c>
@@ -24002,9 +24409,15 @@
         <v>219</v>
       </c>
       <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
+      <c r="G50" s="4">
+        <v>9</v>
+      </c>
+      <c r="H50" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J50" s="4">
         <v>3.705E-2</v>
       </c>
@@ -24012,11 +24425,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>3120014683</v>
       </c>
-      <c r="B51" s="4"/>
+      <c r="B51" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C51" s="4" t="s">
         <v>218</v>
       </c>
@@ -24027,9 +24442,15 @@
         <v>219</v>
       </c>
       <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
+      <c r="G51" s="4">
+        <v>10</v>
+      </c>
+      <c r="H51" s="4">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J51" s="4">
         <v>2.3800000000000002E-2</v>
       </c>
@@ -24037,11 +24458,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>3120014684</v>
       </c>
-      <c r="B52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C52" s="4" t="s">
         <v>220</v>
       </c>
@@ -24052,9 +24475,15 @@
         <v>219</v>
       </c>
       <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
+      <c r="G52" s="4">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J52" s="4">
         <v>2.3800000000000002E-2</v>
       </c>
@@ -24062,11 +24491,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>3120014685</v>
       </c>
-      <c r="B53" s="4"/>
+      <c r="B53" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C53" s="4" t="s">
         <v>220</v>
       </c>
@@ -24077,9 +24508,15 @@
         <v>219</v>
       </c>
       <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
+      <c r="G53" s="4">
+        <v>2</v>
+      </c>
+      <c r="H53" s="4">
+        <v>4.7E-2</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J53" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -24087,11 +24524,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>3120014686</v>
       </c>
-      <c r="B54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C54" s="4" t="s">
         <v>220</v>
       </c>
@@ -24102,9 +24541,15 @@
         <v>219</v>
       </c>
       <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
+      <c r="G54" s="4">
+        <v>3</v>
+      </c>
+      <c r="H54" s="4">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J54" s="4">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -24112,11 +24557,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>3120014728</v>
       </c>
-      <c r="B55" s="4"/>
+      <c r="B55" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C55" s="4" t="s">
         <v>220</v>
       </c>
@@ -24128,10 +24575,14 @@
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4">
-        <v>2</v>
-      </c>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="H55" s="4">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J55" s="4">
         <v>0.32663157450000002</v>
       </c>
@@ -24139,11 +24590,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>3120014728</v>
       </c>
-      <c r="B56" s="4"/>
+      <c r="B56" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C56" s="4" t="s">
         <v>220</v>
       </c>
@@ -24154,9 +24607,15 @@
         <v>222</v>
       </c>
       <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
+      <c r="G56" s="4">
+        <v>5</v>
+      </c>
+      <c r="H56" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J56" s="4">
         <v>4.301088897471167E-2</v>
       </c>
@@ -24164,11 +24623,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>3120014729</v>
       </c>
-      <c r="B57" s="4"/>
+      <c r="B57" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C57" s="4" t="s">
         <v>220</v>
       </c>
@@ -24180,10 +24641,14 @@
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4">
-        <v>2</v>
-      </c>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="H57" s="4">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J57" s="4">
         <v>0.38871856799999999</v>
       </c>
@@ -24191,11 +24656,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>3120014729</v>
       </c>
-      <c r="B58" s="4"/>
+      <c r="B58" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C58" s="4" t="s">
         <v>220</v>
       </c>
@@ -24206,9 +24673,15 @@
         <v>222</v>
       </c>
       <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
+      <c r="G58" s="4">
+        <v>7</v>
+      </c>
+      <c r="H58" s="4">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J58" s="4">
         <v>4.8664648255316363E-2</v>
       </c>
@@ -24216,11 +24689,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>3120014730</v>
       </c>
-      <c r="B59" s="4"/>
+      <c r="B59" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C59" s="4" t="s">
         <v>220</v>
       </c>
@@ -24232,10 +24707,14 @@
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4">
-        <v>2</v>
-      </c>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="H59" s="4">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J59" s="4">
         <v>0.52303176249999983</v>
       </c>
@@ -24243,11 +24722,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>3120014730</v>
       </c>
-      <c r="B60" s="4"/>
+      <c r="B60" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C60" s="4" t="s">
         <v>220</v>
       </c>
@@ -24258,9 +24739,15 @@
         <v>222</v>
       </c>
       <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
+      <c r="G60" s="4">
+        <v>9</v>
+      </c>
+      <c r="H60" s="4">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J60" s="4">
         <v>7.271504848994248E-2</v>
       </c>
@@ -24268,11 +24755,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>3120014731</v>
       </c>
-      <c r="B61" s="4"/>
+      <c r="B61" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C61" s="4" t="s">
         <v>220</v>
       </c>
@@ -24284,10 +24773,14 @@
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4">
-        <v>2</v>
-      </c>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="H61" s="4">
+        <v>5.5E-2</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J61" s="4">
         <v>0.15049128000000001</v>
       </c>
@@ -24295,11 +24788,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>3120014731</v>
       </c>
-      <c r="B62" s="4"/>
+      <c r="B62" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C62" s="4" t="s">
         <v>220</v>
       </c>
@@ -24310,9 +24805,15 @@
         <v>222</v>
       </c>
       <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
+      <c r="G62" s="4">
+        <v>1</v>
+      </c>
+      <c r="H62" s="4">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J62" s="4">
         <v>2.4112500000000009E-2</v>
       </c>
@@ -24320,11 +24821,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>3120014732</v>
       </c>
-      <c r="B63" s="4"/>
+      <c r="B63" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C63" s="4" t="s">
         <v>220</v>
       </c>
@@ -24338,8 +24841,12 @@
       <c r="G63" s="4">
         <v>2</v>
       </c>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
+      <c r="H63" s="4">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J63" s="4">
         <v>0.25246724999999998</v>
       </c>
@@ -24347,11 +24854,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>3120014732</v>
       </c>
-      <c r="B64" s="4"/>
+      <c r="B64" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C64" s="4" t="s">
         <v>220</v>
       </c>
@@ -24362,9 +24871,15 @@
         <v>222</v>
       </c>
       <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
+      <c r="G64" s="4">
+        <v>3</v>
+      </c>
+      <c r="H64" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J64" s="4">
         <v>2.9682E-2</v>
       </c>
@@ -24372,11 +24887,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>3120014733</v>
       </c>
-      <c r="B65" s="4"/>
+      <c r="B65" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C65" s="4" t="s">
         <v>220</v>
       </c>
@@ -24388,10 +24905,14 @@
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4">
-        <v>1</v>
-      </c>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="H65" s="4">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J65" s="4">
         <v>8.5536192864864857E-2</v>
       </c>
@@ -24399,11 +24920,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="17">
         <v>3120014733</v>
       </c>
-      <c r="B66" s="17"/>
+      <c r="B66" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C66" s="17" t="s">
         <v>220</v>
       </c>
@@ -24414,9 +24937,15 @@
         <v>223</v>
       </c>
       <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
+      <c r="G66" s="4">
+        <v>5</v>
+      </c>
+      <c r="H66" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J66" s="17">
         <v>0.22579199999999999</v>
       </c>
@@ -24424,11 +24953,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>3120014733</v>
       </c>
-      <c r="B67" s="4"/>
+      <c r="B67" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C67" s="4" t="s">
         <v>220</v>
       </c>
@@ -24439,9 +24970,15 @@
         <v>224</v>
       </c>
       <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
+      <c r="G67" s="4">
+        <v>6</v>
+      </c>
+      <c r="H67" s="4">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J67" s="4">
         <v>1.6141949999999999E-2</v>
       </c>
@@ -24449,11 +24986,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>3120014734</v>
       </c>
-      <c r="B68" s="4"/>
+      <c r="B68" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C68" s="4" t="s">
         <v>220</v>
       </c>
@@ -24465,10 +25004,14 @@
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4">
-        <v>2</v>
-      </c>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="H68" s="4">
+        <v>6.2E-2</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J68" s="4">
         <v>0.30098256000000012</v>
       </c>
@@ -24476,11 +25019,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>3120014734</v>
       </c>
-      <c r="B69" s="4"/>
+      <c r="B69" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C69" s="4" t="s">
         <v>220</v>
       </c>
@@ -24491,9 +25036,15 @@
         <v>222</v>
       </c>
       <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
+      <c r="G69" s="4">
+        <v>8</v>
+      </c>
+      <c r="H69" s="4">
+        <v>6.3E-2</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J69" s="4">
         <v>4.8224999999999997E-2</v>
       </c>
@@ -24501,11 +25052,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>3120014735</v>
       </c>
-      <c r="B70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C70" s="4" t="s">
         <v>220</v>
       </c>
@@ -24517,10 +25070,14 @@
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4">
-        <v>2</v>
-      </c>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="H70" s="4">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J70" s="4">
         <v>0.50493449999999995</v>
       </c>
@@ -24528,11 +25085,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>3120014735</v>
       </c>
-      <c r="B71" s="4"/>
+      <c r="B71" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C71" s="4" t="s">
         <v>220</v>
       </c>
@@ -24543,9 +25102,15 @@
         <v>222</v>
       </c>
       <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
+      <c r="G71" s="4">
+        <v>10</v>
+      </c>
+      <c r="H71" s="4">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J71" s="4">
         <v>5.9364E-2</v>
       </c>
@@ -24553,11 +25118,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>3120014737</v>
       </c>
-      <c r="B72" s="4"/>
+      <c r="B72" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C72" s="4" t="s">
         <v>220</v>
       </c>
@@ -24569,10 +25136,14 @@
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4">
-        <v>2</v>
-      </c>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H72" s="4">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J72" s="4">
         <v>0.68349514563106795</v>
       </c>
@@ -24580,11 +25151,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>3120014737</v>
       </c>
-      <c r="B73" s="4"/>
+      <c r="B73" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C73" s="4" t="s">
         <v>220</v>
       </c>
@@ -24595,9 +25168,15 @@
         <v>165</v>
       </c>
       <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
+      <c r="G73" s="4">
+        <v>2</v>
+      </c>
+      <c r="H73" s="4">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J73" s="4">
         <v>4.5852001373665519E-2</v>
       </c>
@@ -24605,11 +25184,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>3120014738</v>
       </c>
-      <c r="B74" s="4"/>
+      <c r="B74" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C74" s="4" t="s">
         <v>220</v>
       </c>
@@ -24621,10 +25202,14 @@
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4">
-        <v>2</v>
-      </c>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="H74" s="4">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J74" s="4">
         <v>0.96213592233009704</v>
       </c>
@@ -24632,11 +25217,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>3120014738</v>
       </c>
-      <c r="B75" s="4"/>
+      <c r="B75" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C75" s="4" t="s">
         <v>220</v>
       </c>
@@ -24647,9 +25234,15 @@
         <v>165</v>
       </c>
       <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
+      <c r="G75" s="4">
+        <v>4</v>
+      </c>
+      <c r="H75" s="4">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J75" s="4">
         <v>9.8192230914578849E-2</v>
       </c>
@@ -24657,11 +25250,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>3120014742</v>
       </c>
-      <c r="B76" s="4"/>
+      <c r="B76" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C76" s="4" t="s">
         <v>220</v>
       </c>
@@ -24673,10 +25268,14 @@
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="4">
-        <v>1</v>
-      </c>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="H76" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J76" s="4">
         <v>2.4182599999999999E-2</v>
       </c>
@@ -24684,11 +25283,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="17">
         <v>3120014742</v>
       </c>
-      <c r="B77" s="17"/>
+      <c r="B77" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C77" s="17" t="s">
         <v>220</v>
       </c>
@@ -24699,9 +25300,15 @@
         <v>223</v>
       </c>
       <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
+      <c r="G77" s="4">
+        <v>6</v>
+      </c>
+      <c r="H77" s="4">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J77" s="17">
         <v>7.6888235294117604E-2</v>
       </c>
@@ -24709,11 +25316,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>3120014742</v>
       </c>
-      <c r="B78" s="4"/>
+      <c r="B78" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C78" s="4" t="s">
         <v>220</v>
       </c>
@@ -24724,9 +25333,15 @@
         <v>224</v>
       </c>
       <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
+      <c r="G78" s="4">
+        <v>7</v>
+      </c>
+      <c r="H78" s="4">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J78" s="4">
         <v>4.7117647058823597E-3</v>
       </c>
@@ -24734,11 +25349,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>3120014743</v>
       </c>
-      <c r="B79" s="4"/>
+      <c r="B79" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C79" s="4" t="s">
         <v>220</v>
       </c>
@@ -24750,10 +25367,14 @@
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4">
-        <v>1</v>
-      </c>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="H79" s="4">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J79" s="4">
         <v>4.7290079999999998E-2</v>
       </c>
@@ -24761,11 +25382,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="17">
         <v>3120014743</v>
       </c>
-      <c r="B80" s="17"/>
+      <c r="B80" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C80" s="17" t="s">
         <v>220</v>
       </c>
@@ -24776,9 +25399,15 @@
         <v>223</v>
       </c>
       <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
+      <c r="G80" s="4">
+        <v>9</v>
+      </c>
+      <c r="H80" s="4">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J80" s="17">
         <v>7.1011764705882358E-2</v>
       </c>
@@ -24786,11 +25415,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>3120014743</v>
       </c>
-      <c r="B81" s="4"/>
+      <c r="B81" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C81" s="4" t="s">
         <v>220</v>
       </c>
@@ -24801,9 +25432,15 @@
         <v>224</v>
       </c>
       <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
+      <c r="G81" s="4">
+        <v>10</v>
+      </c>
+      <c r="H81" s="4">
+        <v>7.5000000000000094E-2</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J81" s="4">
         <v>8.7882352941176453E-3</v>
       </c>
@@ -24811,11 +25448,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>3120014744</v>
       </c>
-      <c r="B82" s="4"/>
+      <c r="B82" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C82" s="4" t="s">
         <v>218</v>
       </c>
@@ -24829,8 +25468,12 @@
       <c r="G82" s="4">
         <v>1</v>
       </c>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
+      <c r="H82" s="4">
+        <v>7.6000000000000095E-2</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J82" s="4">
         <v>2.4138400000000001E-2</v>
       </c>
@@ -24838,11 +25481,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="17">
         <v>3120014744</v>
       </c>
-      <c r="B83" s="17"/>
+      <c r="B83" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C83" s="17" t="s">
         <v>218</v>
       </c>
@@ -24853,9 +25498,15 @@
         <v>223</v>
       </c>
       <c r="F83" s="17"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
+      <c r="G83" s="4">
+        <v>2</v>
+      </c>
+      <c r="H83" s="4">
+        <v>7.7000000000000096E-2</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J83" s="17">
         <v>7.6888235294117646E-2</v>
       </c>
@@ -24863,11 +25514,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>3120014744</v>
       </c>
-      <c r="B84" s="4"/>
+      <c r="B84" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C84" s="4" t="s">
         <v>220</v>
       </c>
@@ -24878,9 +25531,15 @@
         <v>224</v>
       </c>
       <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
+      <c r="G84" s="4">
+        <v>3</v>
+      </c>
+      <c r="H84" s="4">
+        <v>7.8000000000000097E-2</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J84" s="4">
         <v>4.7117647058823563E-3</v>
       </c>
@@ -24888,11 +25547,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>3120014745</v>
       </c>
-      <c r="B85" s="4"/>
+      <c r="B85" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C85" s="4" t="s">
         <v>220</v>
       </c>
@@ -24903,9 +25564,15 @@
         <v>219</v>
       </c>
       <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
+      <c r="G85" s="4">
+        <v>4</v>
+      </c>
+      <c r="H85" s="4">
+        <v>7.9000000000000098E-2</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J85" s="4">
         <v>2.6700000000000002E-2</v>
       </c>
@@ -24913,11 +25580,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>3120014747</v>
       </c>
-      <c r="B86" s="4"/>
+      <c r="B86" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C86" s="4" t="s">
         <v>220</v>
       </c>
@@ -24929,10 +25598,14 @@
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4">
-        <v>2</v>
-      </c>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="H86" s="4">
+        <v>8.0000000000000099E-2</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J86" s="4">
         <v>0.77743713599999997</v>
       </c>
@@ -24940,11 +25613,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>3120014747</v>
       </c>
-      <c r="B87" s="4"/>
+      <c r="B87" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C87" s="4" t="s">
         <v>218</v>
       </c>
@@ -24955,9 +25630,15 @@
         <v>222</v>
       </c>
       <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
+      <c r="G87" s="4">
+        <v>6</v>
+      </c>
+      <c r="H87" s="4">
+        <v>8.10000000000001E-2</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J87" s="4">
         <v>9.7329296510632712E-2</v>
       </c>
@@ -24965,11 +25646,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>3120014748</v>
       </c>
-      <c r="B88" s="4"/>
+      <c r="B88" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C88" s="4" t="s">
         <v>220</v>
       </c>
@@ -24981,10 +25664,14 @@
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4">
-        <v>2</v>
-      </c>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="H88" s="4">
+        <v>8.2000000000000101E-2</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J88" s="4">
         <v>1.0460635250000001</v>
       </c>
@@ -24992,11 +25679,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>3120014748</v>
       </c>
-      <c r="B89" s="4"/>
+      <c r="B89" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C89" s="4" t="s">
         <v>218</v>
       </c>
@@ -25007,9 +25696,15 @@
         <v>222</v>
       </c>
       <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
+      <c r="G89" s="4">
+        <v>8</v>
+      </c>
+      <c r="H89" s="4">
+        <v>8.3000000000000101E-2</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J89" s="4">
         <v>0.14543009697988499</v>
       </c>
@@ -25017,11 +25712,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>3120014754</v>
       </c>
-      <c r="B90" s="4"/>
+      <c r="B90" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C90" s="4" t="s">
         <v>220</v>
       </c>
@@ -25033,10 +25730,14 @@
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4">
-        <v>1</v>
-      </c>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="H90" s="4">
+        <v>8.4000000000000102E-2</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J90" s="4">
         <v>9.0616000000000002E-2</v>
       </c>
@@ -25044,11 +25745,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="17">
         <v>3120014754</v>
       </c>
-      <c r="B91" s="17"/>
+      <c r="B91" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C91" s="17" t="s">
         <v>220</v>
       </c>
@@ -25059,9 +25762,15 @@
         <v>223</v>
       </c>
       <c r="F91" s="17"/>
-      <c r="G91" s="17"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
+      <c r="G91" s="4">
+        <v>10</v>
+      </c>
+      <c r="H91" s="4">
+        <v>8.5000000000000103E-2</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J91" s="17">
         <v>0.1078117647058824</v>
       </c>
@@ -25069,11 +25778,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>3120014754</v>
       </c>
-      <c r="B92" s="4"/>
+      <c r="B92" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C92" s="4" t="s">
         <v>220</v>
       </c>
@@ -25084,9 +25795,15 @@
         <v>224</v>
       </c>
       <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
+      <c r="G92" s="4">
+        <v>1</v>
+      </c>
+      <c r="H92" s="4">
+        <v>8.6000000000000104E-2</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J92" s="4">
         <v>1.8628235294117661E-2</v>
       </c>
@@ -25094,11 +25811,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>3120014756</v>
       </c>
-      <c r="B93" s="4"/>
+      <c r="B93" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C93" s="4" t="s">
         <v>220</v>
       </c>
@@ -25112,8 +25831,12 @@
       <c r="G93" s="4">
         <v>2</v>
       </c>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
+      <c r="H93" s="4">
+        <v>8.7000000000000105E-2</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J93" s="4">
         <v>1.3669902912621359</v>
       </c>
@@ -25121,11 +25844,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>3120014756</v>
       </c>
-      <c r="B94" s="4"/>
+      <c r="B94" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C94" s="4" t="s">
         <v>220</v>
       </c>
@@ -25136,9 +25861,15 @@
         <v>222</v>
       </c>
       <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
+      <c r="G94" s="4">
+        <v>3</v>
+      </c>
+      <c r="H94" s="4">
+        <v>8.8000000000000106E-2</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J94" s="4">
         <v>9.1704002747331037E-2</v>
       </c>
@@ -25146,11 +25877,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>3120014757</v>
       </c>
-      <c r="B95" s="4"/>
+      <c r="B95" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C95" s="4" t="s">
         <v>220</v>
       </c>
@@ -25162,10 +25895,14 @@
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4">
-        <v>2</v>
-      </c>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="H95" s="4">
+        <v>8.9000000000000107E-2</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J95" s="4">
         <v>1.9242718446601941</v>
       </c>
@@ -25173,11 +25910,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>3120014757</v>
       </c>
-      <c r="B96" s="4"/>
+      <c r="B96" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C96" s="4" t="s">
         <v>220</v>
       </c>
@@ -25188,9 +25927,15 @@
         <v>222</v>
       </c>
       <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
+      <c r="G96" s="4">
+        <v>5</v>
+      </c>
+      <c r="H96" s="4">
+        <v>9.0000000000000094E-2</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J96" s="4">
         <v>0.1963844618291577</v>
       </c>
@@ -25198,11 +25943,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>3120014823</v>
       </c>
-      <c r="B97" s="4"/>
+      <c r="B97" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C97" s="4" t="s">
         <v>220</v>
       </c>
@@ -25213,9 +25960,15 @@
         <v>219</v>
       </c>
       <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
+      <c r="G97" s="4">
+        <v>6</v>
+      </c>
+      <c r="H97" s="4">
+        <v>9.1000000000000095E-2</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J97" s="4">
         <v>2.6700000000000002E-2</v>
       </c>
@@ -25223,11 +25976,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>3120014824</v>
       </c>
-      <c r="B98" s="4"/>
+      <c r="B98" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C98" s="4" t="s">
         <v>218</v>
       </c>
@@ -25238,9 +25993,15 @@
         <v>219</v>
       </c>
       <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
+      <c r="G98" s="4">
+        <v>7</v>
+      </c>
+      <c r="H98" s="4">
+        <v>9.2000000000000096E-2</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J98" s="4">
         <v>2.6700000000000002E-2</v>
       </c>
@@ -25248,11 +26009,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>3120014825</v>
       </c>
-      <c r="B99" s="4"/>
+      <c r="B99" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C99" s="4" t="s">
         <v>220</v>
       </c>
@@ -25263,9 +26026,15 @@
         <v>219</v>
       </c>
       <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
+      <c r="G99" s="4">
+        <v>8</v>
+      </c>
+      <c r="H99" s="4">
+        <v>9.3000000000000096E-2</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J99" s="4">
         <v>2.6700000000000002E-2</v>
       </c>
@@ -25273,11 +26042,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>3120014826</v>
       </c>
-      <c r="B100" s="4"/>
+      <c r="B100" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C100" s="4" t="s">
         <v>220</v>
       </c>
@@ -25288,9 +26059,15 @@
         <v>219</v>
       </c>
       <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
+      <c r="G100" s="4">
+        <v>9</v>
+      </c>
+      <c r="H100" s="4">
+        <v>9.4000000000000097E-2</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J100" s="4">
         <v>2.6700000000000002E-2</v>
       </c>
@@ -25298,11 +26075,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>3120014827</v>
       </c>
-      <c r="B101" s="4"/>
+      <c r="B101" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C101" s="4" t="s">
         <v>220</v>
       </c>
@@ -25314,10 +26093,14 @@
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4">
-        <v>1</v>
-      </c>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="H101" s="4">
+        <v>9.5000000000000098E-2</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J101" s="4">
         <v>2.5479999999999999E-2</v>
       </c>
@@ -25325,11 +26108,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="17">
         <v>3120014827</v>
       </c>
-      <c r="B102" s="17"/>
+      <c r="B102" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C102" s="17" t="s">
         <v>220</v>
       </c>
@@ -25340,9 +26125,15 @@
         <v>223</v>
       </c>
       <c r="F102" s="17"/>
-      <c r="G102" s="17"/>
-      <c r="H102" s="17"/>
-      <c r="I102" s="17"/>
+      <c r="G102" s="4">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4">
+        <v>9.6000000000000099E-2</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J102" s="17">
         <v>7.6888235294117646E-2</v>
       </c>
@@ -25350,11 +26141,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>3120014827</v>
       </c>
-      <c r="B103" s="4"/>
+      <c r="B103" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C103" s="4" t="s">
         <v>220</v>
       </c>
@@ -25365,9 +26158,15 @@
         <v>224</v>
       </c>
       <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
+      <c r="G103" s="4">
+        <v>2</v>
+      </c>
+      <c r="H103" s="4">
+        <v>9.70000000000001E-2</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J103" s="4">
         <v>4.7117647058823563E-3</v>
       </c>
@@ -25375,11 +26174,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>3120015057</v>
       </c>
-      <c r="B104" s="4"/>
+      <c r="B104" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C104" s="4" t="s">
         <v>220</v>
       </c>
@@ -25393,8 +26194,12 @@
       <c r="G104" s="4">
         <v>3</v>
       </c>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
+      <c r="H104" s="4">
+        <v>9.8000000000000101E-2</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J104" s="4">
         <v>0.50634687743999995</v>
       </c>
@@ -25402,11 +26207,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>3120015057</v>
       </c>
-      <c r="B105" s="4"/>
+      <c r="B105" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C105" s="4" t="s">
         <v>218</v>
       </c>
@@ -25417,9 +26224,15 @@
         <v>222</v>
       </c>
       <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
+      <c r="G105" s="4">
+        <v>4</v>
+      </c>
+      <c r="H105" s="4">
+        <v>9.9000000000000102E-2</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J105" s="4">
         <v>6.5609026560000006E-2</v>
       </c>
@@ -25427,11 +26240,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>3120015084</v>
       </c>
-      <c r="B106" s="4"/>
+      <c r="B106" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C106" s="4" t="s">
         <v>220</v>
       </c>
@@ -25442,9 +26257,15 @@
         <v>219</v>
       </c>
       <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
+      <c r="G106" s="4">
+        <v>5</v>
+      </c>
+      <c r="H106" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J106" s="4">
         <v>8.5907250000000004E-2</v>
       </c>
@@ -25452,11 +26273,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>3120015084</v>
       </c>
-      <c r="B107" s="4"/>
+      <c r="B107" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C107" s="4" t="s">
         <v>218</v>
       </c>
@@ -25467,9 +26290,15 @@
         <v>223</v>
       </c>
       <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
+      <c r="G107" s="4">
+        <v>6</v>
+      </c>
+      <c r="H107" s="4">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J107" s="4">
         <v>0.25731199999999999</v>
       </c>
@@ -25477,11 +26306,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>3120015085</v>
       </c>
-      <c r="B108" s="4"/>
+      <c r="B108" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C108" s="4" t="s">
         <v>220</v>
       </c>
@@ -25492,9 +26323,15 @@
         <v>219</v>
       </c>
       <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
+      <c r="G108" s="4">
+        <v>7</v>
+      </c>
+      <c r="H108" s="4">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J108" s="4">
         <v>0.16975860000000001</v>
       </c>
@@ -25502,11 +26339,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>3120015085</v>
       </c>
-      <c r="B109" s="4"/>
+      <c r="B109" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C109" s="4" t="s">
         <v>220</v>
       </c>
@@ -25517,9 +26356,15 @@
         <v>223</v>
       </c>
       <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
+      <c r="G109" s="4">
+        <v>8</v>
+      </c>
+      <c r="H109" s="4">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J109" s="4">
         <v>0.37564799999999998</v>
       </c>
@@ -25527,11 +26372,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>3120015391</v>
       </c>
-      <c r="B110" s="4"/>
+      <c r="B110" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C110" s="4" t="s">
         <v>220</v>
       </c>
@@ -25543,10 +26390,14 @@
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4">
-        <v>3</v>
-      </c>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="H110" s="4">
+        <v>0.104</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J110" s="4">
         <v>0.1113</v>
       </c>
@@ -25554,11 +26405,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>3120015391</v>
       </c>
-      <c r="B111" s="4"/>
+      <c r="B111" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C111" s="4" t="s">
         <v>218</v>
       </c>
@@ -25569,9 +26422,15 @@
         <v>222</v>
       </c>
       <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
+      <c r="G111" s="4">
+        <v>10</v>
+      </c>
+      <c r="H111" s="4">
+        <v>0.105</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J111" s="4">
         <v>1.4134815749999989E-2</v>
       </c>
@@ -25579,11 +26438,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>3120015392</v>
       </c>
-      <c r="B112" s="4"/>
+      <c r="B112" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C112" s="4" t="s">
         <v>220</v>
       </c>
@@ -25595,10 +26456,14 @@
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4">
-        <v>3</v>
-      </c>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H112" s="4">
+        <v>0.106</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J112" s="4">
         <v>0.10793288249999999</v>
       </c>
@@ -25606,11 +26471,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>3120015392</v>
       </c>
-      <c r="B113" s="4"/>
+      <c r="B113" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C113" s="4" t="s">
         <v>220</v>
       </c>
@@ -25621,9 +26488,15 @@
         <v>222</v>
       </c>
       <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
+      <c r="G113" s="4">
+        <v>2</v>
+      </c>
+      <c r="H113" s="4">
+        <v>0.107</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J113" s="4">
         <v>1.4134815749999989E-2</v>
       </c>
@@ -25631,11 +26504,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>3120015393</v>
       </c>
-      <c r="B114" s="4"/>
+      <c r="B114" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C114" s="4" t="s">
         <v>220</v>
       </c>
@@ -25649,8 +26524,12 @@
       <c r="G114" s="4">
         <v>3</v>
       </c>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
+      <c r="H114" s="4">
+        <v>0.108</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J114" s="4">
         <v>7.5200000000000003E-2</v>
       </c>
@@ -25658,11 +26537,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>3120015393</v>
       </c>
-      <c r="B115" s="4"/>
+      <c r="B115" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C115" s="4" t="s">
         <v>220</v>
       </c>
@@ -25673,9 +26554,15 @@
         <v>224</v>
       </c>
       <c r="F115" s="4"/>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
-      <c r="I115" s="4"/>
+      <c r="G115" s="4">
+        <v>4</v>
+      </c>
+      <c r="H115" s="4">
+        <v>0.109</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J115" s="4">
         <v>8.9092171999999997E-3</v>
       </c>
@@ -25683,11 +26570,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>3120016298</v>
       </c>
-      <c r="B116" s="4"/>
+      <c r="B116" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C116" s="4" t="s">
         <v>220</v>
       </c>
@@ -25699,10 +26588,14 @@
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="4">
-        <v>2</v>
-      </c>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="H116" s="4">
+        <v>0.11</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J116" s="4">
         <v>0.65326314900000004</v>
       </c>
@@ -25710,11 +26603,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>3120016298</v>
       </c>
-      <c r="B117" s="4"/>
+      <c r="B117" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C117" s="4" t="s">
         <v>220</v>
       </c>
@@ -25725,9 +26620,15 @@
         <v>222</v>
       </c>
       <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
+      <c r="G117" s="4">
+        <v>6</v>
+      </c>
+      <c r="H117" s="4">
+        <v>0.111</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J117" s="4">
         <v>8.6021777949423339E-2</v>
       </c>
@@ -25735,11 +26636,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>3120016450</v>
       </c>
-      <c r="B118" s="4"/>
+      <c r="B118" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C118" s="4" t="s">
         <v>220</v>
       </c>
@@ -25751,10 +26654,14 @@
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="4">
-        <v>2</v>
-      </c>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="H118" s="4">
+        <v>0.112</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J118" s="4">
         <v>0.30098256000000012</v>
       </c>
@@ -25762,11 +26669,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>3120016450</v>
       </c>
-      <c r="B119" s="4"/>
+      <c r="B119" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C119" s="4" t="s">
         <v>220</v>
       </c>
@@ -25777,9 +26686,15 @@
         <v>222</v>
       </c>
       <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
+      <c r="G119" s="4">
+        <v>8</v>
+      </c>
+      <c r="H119" s="4">
+        <v>0.113</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J119" s="4">
         <v>4.8224999999999997E-2</v>
       </c>
@@ -25787,11 +26702,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>3121010037</v>
       </c>
-      <c r="B120" s="4"/>
+      <c r="B120" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C120" s="4" t="s">
         <v>220</v>
       </c>
@@ -25802,9 +26719,15 @@
         <v>219</v>
       </c>
       <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
+      <c r="G120" s="4">
+        <v>9</v>
+      </c>
+      <c r="H120" s="4">
+        <v>0.114</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J120" s="4">
         <v>4.8000000000000001E-2</v>
       </c>
@@ -25812,11 +26735,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>3121010038</v>
       </c>
-      <c r="B121" s="4"/>
+      <c r="B121" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C121" s="4" t="s">
         <v>220</v>
       </c>
@@ -25827,9 +26752,15 @@
         <v>219</v>
       </c>
       <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
+      <c r="G121" s="4">
+        <v>10</v>
+      </c>
+      <c r="H121" s="4">
+        <v>0.115</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J121" s="4">
         <v>3.5700000000000003E-2</v>
       </c>
@@ -25837,11 +26768,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>3121010039</v>
       </c>
-      <c r="B122" s="4"/>
+      <c r="B122" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C122" s="4" t="s">
         <v>218</v>
       </c>
@@ -25852,9 +26785,15 @@
         <v>58</v>
       </c>
       <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
+      <c r="G122" s="4">
+        <v>1</v>
+      </c>
+      <c r="H122" s="4">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J122" s="4">
         <v>1.388E-2</v>
       </c>
@@ -25862,11 +26801,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>3121010124</v>
       </c>
-      <c r="B123" s="4"/>
+      <c r="B123" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C123" s="4" t="s">
         <v>220</v>
       </c>
@@ -25878,10 +26819,14 @@
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="4">
-        <v>1</v>
-      </c>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="H123" s="4">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J123" s="4">
         <v>4.3119999999999999E-2</v>
       </c>
@@ -25889,11 +26834,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="17">
         <v>3121010124</v>
       </c>
-      <c r="B124" s="17"/>
+      <c r="B124" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C124" s="17" t="s">
         <v>220</v>
       </c>
@@ -25904,9 +26851,15 @@
         <v>223</v>
       </c>
       <c r="F124" s="17"/>
-      <c r="G124" s="17"/>
-      <c r="H124" s="17"/>
-      <c r="I124" s="17"/>
+      <c r="G124" s="4">
+        <v>3</v>
+      </c>
+      <c r="H124" s="4">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J124" s="17">
         <v>9.7988235294117598E-2</v>
       </c>
@@ -25914,11 +26867,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>3121010124</v>
       </c>
-      <c r="B125" s="4"/>
+      <c r="B125" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C125" s="4" t="s">
         <v>220</v>
       </c>
@@ -25929,9 +26884,15 @@
         <v>224</v>
       </c>
       <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
+      <c r="G125" s="4">
+        <v>4</v>
+      </c>
+      <c r="H125" s="4">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J125" s="4">
         <v>1.4611764705882361E-2</v>
       </c>
@@ -25939,11 +26900,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>3121010125</v>
       </c>
-      <c r="B126" s="4"/>
+      <c r="B126" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C126" s="4" t="s">
         <v>220</v>
       </c>
@@ -25955,10 +26918,14 @@
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="4">
-        <v>1</v>
-      </c>
-      <c r="H126" s="4"/>
-      <c r="I126" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="H126" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J126" s="4">
         <v>4.19408E-2</v>
       </c>
@@ -25966,11 +26933,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="17">
         <v>3121010125</v>
       </c>
-      <c r="B127" s="17"/>
+      <c r="B127" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C127" s="17" t="s">
         <v>220</v>
       </c>
@@ -25981,9 +26950,15 @@
         <v>223</v>
       </c>
       <c r="F127" s="17"/>
-      <c r="G127" s="17"/>
-      <c r="H127" s="17"/>
-      <c r="I127" s="17"/>
+      <c r="G127" s="4">
+        <v>6</v>
+      </c>
+      <c r="H127" s="4">
+        <v>0.121</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J127" s="17">
         <v>0.12845882352941179</v>
       </c>
@@ -25991,11 +26966,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>3121010125</v>
       </c>
-      <c r="B128" s="4"/>
+      <c r="B128" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C128" s="4" t="s">
         <v>220</v>
       </c>
@@ -26006,9 +26983,15 @@
         <v>224</v>
       </c>
       <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
+      <c r="G128" s="4">
+        <v>7</v>
+      </c>
+      <c r="H128" s="4">
+        <v>0.122</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J128" s="4">
         <v>1.4611764705882361E-2</v>
       </c>
@@ -26016,11 +26999,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>3121010126</v>
       </c>
-      <c r="B129" s="4"/>
+      <c r="B129" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C129" s="4" t="s">
         <v>220</v>
       </c>
@@ -26032,10 +27017,14 @@
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4">
-        <v>1</v>
-      </c>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="H129" s="4">
+        <v>0.123</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J129" s="4">
         <v>0.17340808648648651</v>
       </c>
@@ -26043,11 +27032,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>3121010126</v>
       </c>
-      <c r="B130" s="4"/>
+      <c r="B130" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C130" s="4" t="s">
         <v>220</v>
       </c>
@@ -26058,9 +27049,15 @@
         <v>170</v>
       </c>
       <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
+      <c r="G130" s="4">
+        <v>9</v>
+      </c>
+      <c r="H130" s="4">
+        <v>0.124</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J130" s="4">
         <v>0.3635968</v>
       </c>
@@ -26068,11 +27065,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>3121010126</v>
       </c>
-      <c r="B131" s="4"/>
+      <c r="B131" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C131" s="4" t="s">
         <v>218</v>
       </c>
@@ -26083,9 +27082,15 @@
         <v>225</v>
       </c>
       <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
+      <c r="G131" s="4">
+        <v>10</v>
+      </c>
+      <c r="H131" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J131" s="4">
         <v>3.1482000000000003E-2</v>
       </c>
@@ -26093,11 +27098,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>3121010128</v>
       </c>
-      <c r="B132" s="4"/>
+      <c r="B132" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C132" s="4" t="s">
         <v>218</v>
       </c>
@@ -26111,8 +27118,12 @@
       <c r="G132" s="4">
         <v>1</v>
       </c>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
+      <c r="H132" s="4">
+        <v>0.126</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J132" s="4">
         <v>4.3119999999999999E-2</v>
       </c>
@@ -26120,11 +27131,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="17">
         <v>3121010128</v>
       </c>
-      <c r="B133" s="17"/>
+      <c r="B133" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C133" s="17" t="s">
         <v>218</v>
       </c>
@@ -26135,9 +27148,15 @@
         <v>226</v>
       </c>
       <c r="F133" s="17"/>
-      <c r="G133" s="17"/>
-      <c r="H133" s="17"/>
-      <c r="I133" s="17"/>
+      <c r="G133" s="4">
+        <v>2</v>
+      </c>
+      <c r="H133" s="4">
+        <v>0.127</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J133" s="17">
         <v>9.7988235294117598E-2</v>
       </c>
@@ -26145,11 +27164,13 @@
         <v>227</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>3121010128</v>
       </c>
-      <c r="B134" s="4"/>
+      <c r="B134" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C134" s="4" t="s">
         <v>228</v>
       </c>
@@ -26160,9 +27181,15 @@
         <v>224</v>
       </c>
       <c r="F134" s="4"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
+      <c r="G134" s="4">
+        <v>3</v>
+      </c>
+      <c r="H134" s="4">
+        <v>0.128</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J134" s="4">
         <v>1.4611764705882361E-2</v>
       </c>
@@ -26170,11 +27197,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>3121010135</v>
       </c>
-      <c r="B135" s="4"/>
+      <c r="B135" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C135" s="4" t="s">
         <v>220</v>
       </c>
@@ -26185,9 +27214,15 @@
         <v>219</v>
       </c>
       <c r="F135" s="4"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
+      <c r="G135" s="4">
+        <v>4</v>
+      </c>
+      <c r="H135" s="4">
+        <v>0.129</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J135" s="4">
         <v>4.1399999999999999E-2</v>
       </c>
@@ -26195,11 +27230,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>3121010283</v>
       </c>
-      <c r="B136" s="4"/>
+      <c r="B136" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C136" s="4" t="s">
         <v>220</v>
       </c>
@@ -26210,9 +27247,15 @@
         <v>58</v>
       </c>
       <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
+      <c r="G136" s="4">
+        <v>5</v>
+      </c>
+      <c r="H136" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="I136" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J136" s="4">
         <v>6.3879749999999999E-2</v>
       </c>
@@ -26220,11 +27263,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>3121010283</v>
       </c>
-      <c r="B137" s="4"/>
+      <c r="B137" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C137" s="4" t="s">
         <v>220</v>
       </c>
@@ -26235,9 +27280,15 @@
         <v>223</v>
       </c>
       <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
+      <c r="G137" s="4">
+        <v>6</v>
+      </c>
+      <c r="H137" s="4">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J137" s="4">
         <v>0.139234</v>
       </c>
@@ -26245,11 +27296,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>3121010284</v>
       </c>
-      <c r="B138" s="4"/>
+      <c r="B138" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C138" s="4" t="s">
         <v>220</v>
       </c>
@@ -26260,9 +27313,15 @@
         <v>219</v>
       </c>
       <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
+      <c r="G138" s="4">
+        <v>7</v>
+      </c>
+      <c r="H138" s="4">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J138" s="4">
         <v>0.12291344999999999</v>
       </c>
@@ -26270,11 +27329,13 @@
         <v>221</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>3121010284</v>
       </c>
-      <c r="B139" s="4"/>
+      <c r="B139" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="C139" s="4" t="s">
         <v>220</v>
       </c>
@@ -26285,9 +27346,15 @@
         <v>223</v>
       </c>
       <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
+      <c r="G139" s="4">
+        <v>8</v>
+      </c>
+      <c r="H139" s="4">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="J139" s="4">
         <v>0.377884</v>
       </c>
@@ -26299,7 +27366,9 @@
       <c r="A140" s="4">
         <v>3120010019</v>
       </c>
-      <c r="B140" s="4"/>
+      <c r="B140" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C140" s="4" t="s">
         <v>229</v>
       </c>
@@ -26312,17 +27381,29 @@
       <c r="F140" s="4">
         <v>100</v>
       </c>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
-      <c r="K140" s="4"/>
+      <c r="G140" s="4">
+        <v>9</v>
+      </c>
+      <c r="H140" s="4">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="I140" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J140" s="4">
+        <v>0.111225</v>
+      </c>
+      <c r="K140" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="141" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>3120011179</v>
       </c>
-      <c r="B141" s="4"/>
+      <c r="B141" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C141" s="4" t="s">
         <v>229</v>
       </c>
@@ -26335,17 +27416,29 @@
       <c r="F141" s="4">
         <v>100</v>
       </c>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="4"/>
-      <c r="K141" s="4"/>
+      <c r="G141" s="4">
+        <v>10</v>
+      </c>
+      <c r="H141" s="4">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J141" s="4">
+        <v>0.11226</v>
+      </c>
+      <c r="K141" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="142" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>3120011180</v>
       </c>
-      <c r="B142" s="4"/>
+      <c r="B142" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C142" s="4" t="s">
         <v>229</v>
       </c>
@@ -26358,17 +27451,29 @@
       <c r="F142" s="4">
         <v>100</v>
       </c>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="4"/>
-      <c r="K142" s="4"/>
+      <c r="G142" s="4">
+        <v>1</v>
+      </c>
+      <c r="H142" s="4">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J142" s="4">
+        <v>0.11329500000000001</v>
+      </c>
+      <c r="K142" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="143" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>3120011622</v>
       </c>
-      <c r="B143" s="4"/>
+      <c r="B143" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C143" s="4" t="s">
         <v>229</v>
       </c>
@@ -26381,17 +27486,29 @@
       <c r="F143" s="4">
         <v>100</v>
       </c>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
-      <c r="K143" s="4"/>
+      <c r="G143" s="4">
+        <v>2</v>
+      </c>
+      <c r="H143" s="4">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J143" s="4">
+        <v>0.11433</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="144" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>3120011785</v>
       </c>
-      <c r="B144" s="4"/>
+      <c r="B144" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C144" s="4" t="s">
         <v>229</v>
       </c>
@@ -26404,17 +27521,29 @@
       <c r="F144" s="4">
         <v>100</v>
       </c>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="4"/>
-      <c r="K144" s="4"/>
+      <c r="G144" s="4">
+        <v>3</v>
+      </c>
+      <c r="H144" s="4">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J144" s="4">
+        <v>0.115365</v>
+      </c>
+      <c r="K144" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="145" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>3120014677</v>
       </c>
-      <c r="B145" s="4"/>
+      <c r="B145" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C145" s="4" t="s">
         <v>229</v>
       </c>
@@ -26427,17 +27556,29 @@
       <c r="F145" s="4">
         <v>100</v>
       </c>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
-      <c r="K145" s="4"/>
-    </row>
-    <row r="146" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G145" s="4">
+        <v>4</v>
+      </c>
+      <c r="H145" s="4">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J145" s="4">
+        <v>0.1164</v>
+      </c>
+      <c r="K145" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>3120014678</v>
       </c>
-      <c r="B146" s="4"/>
+      <c r="B146" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C146" s="4" t="s">
         <v>170</v>
       </c>
@@ -26450,17 +27591,29 @@
       <c r="F146" s="4">
         <v>100</v>
       </c>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
-      <c r="K146" s="4"/>
-    </row>
-    <row r="147" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G146" s="4">
+        <v>5</v>
+      </c>
+      <c r="H146" s="4">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J146" s="4">
+        <v>0.117435</v>
+      </c>
+      <c r="K146" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>3120014679</v>
       </c>
-      <c r="B147" s="4"/>
+      <c r="B147" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C147" s="4" t="s">
         <v>230</v>
       </c>
@@ -26473,17 +27626,29 @@
       <c r="F147" s="4">
         <v>63</v>
       </c>
-      <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
-      <c r="I147" s="4"/>
-      <c r="J147" s="4"/>
-      <c r="K147" s="4"/>
-    </row>
-    <row r="148" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G147" s="4">
+        <v>6</v>
+      </c>
+      <c r="H147" s="4">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J147" s="4">
+        <v>0.11847000000000001</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>3120014679</v>
       </c>
-      <c r="B148" s="4"/>
+      <c r="B148" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C148" s="4" t="s">
         <v>230</v>
       </c>
@@ -26496,17 +27661,29 @@
       <c r="F148" s="4">
         <v>37</v>
       </c>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
-      <c r="K148" s="4"/>
-    </row>
-    <row r="149" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G148" s="4">
+        <v>7</v>
+      </c>
+      <c r="H148" s="4">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J148" s="4">
+        <v>0.119505</v>
+      </c>
+      <c r="K148" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>3120014680</v>
       </c>
-      <c r="B149" s="4"/>
+      <c r="B149" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C149" s="4" t="s">
         <v>170</v>
       </c>
@@ -26519,17 +27696,29 @@
       <c r="F149" s="4">
         <v>100</v>
       </c>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
-      <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
-      <c r="K149" s="4"/>
-    </row>
-    <row r="150" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G149" s="4">
+        <v>8</v>
+      </c>
+      <c r="H149" s="4">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J149" s="4">
+        <v>0.12053999999999999</v>
+      </c>
+      <c r="K149" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>3120014682</v>
       </c>
-      <c r="B150" s="4"/>
+      <c r="B150" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C150" s="4" t="s">
         <v>161</v>
       </c>
@@ -26542,17 +27731,29 @@
       <c r="F150" s="4">
         <v>100</v>
       </c>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
-      <c r="I150" s="4"/>
-      <c r="J150" s="4"/>
-      <c r="K150" s="4"/>
-    </row>
-    <row r="151" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G150" s="4">
+        <v>9</v>
+      </c>
+      <c r="H150" s="4">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J150" s="4">
+        <v>0.121575</v>
+      </c>
+      <c r="K150" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>3120014683</v>
       </c>
-      <c r="B151" s="4"/>
+      <c r="B151" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C151" s="4" t="s">
         <v>170</v>
       </c>
@@ -26565,17 +27766,29 @@
       <c r="F151" s="4">
         <v>100</v>
       </c>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
-      <c r="I151" s="4"/>
-      <c r="J151" s="4"/>
-      <c r="K151" s="4"/>
-    </row>
-    <row r="152" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G151" s="4">
+        <v>10</v>
+      </c>
+      <c r="H151" s="4">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J151" s="4">
+        <v>0.12261</v>
+      </c>
+      <c r="K151" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>3120014684</v>
       </c>
-      <c r="B152" s="4"/>
+      <c r="B152" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C152" s="4" t="s">
         <v>170</v>
       </c>
@@ -26588,13 +27801,23 @@
       <c r="F152" s="4">
         <v>100</v>
       </c>
-      <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
-      <c r="K152" s="4"/>
-    </row>
-    <row r="153" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G152" s="4">
+        <v>1</v>
+      </c>
+      <c r="H152" s="4">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J152" s="4">
+        <v>0.123645</v>
+      </c>
+      <c r="K152" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>3120014685</v>
       </c>
@@ -26611,13 +27834,23 @@
       <c r="F153" s="4">
         <v>100</v>
       </c>
-      <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
-      <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
-      <c r="K153" s="4"/>
-    </row>
-    <row r="154" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G153" s="4">
+        <v>2</v>
+      </c>
+      <c r="H153" s="4">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J153" s="4">
+        <v>0.12468</v>
+      </c>
+      <c r="K153" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>3120014686</v>
       </c>
@@ -26634,17 +27867,29 @@
       <c r="F154" s="4">
         <v>100</v>
       </c>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
-      <c r="K154" s="4"/>
-    </row>
-    <row r="155" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G154" s="4">
+        <v>3</v>
+      </c>
+      <c r="H154" s="4">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J154" s="4">
+        <v>0.12571499999999999</v>
+      </c>
+      <c r="K154" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>3120014728</v>
       </c>
-      <c r="B155" s="4"/>
+      <c r="B155" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C155" s="4" t="s">
         <v>230</v>
       </c>
@@ -26657,17 +27902,29 @@
       <c r="F155" s="4">
         <v>63</v>
       </c>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
-      <c r="K155" s="4"/>
-    </row>
-    <row r="156" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G155" s="4">
+        <v>4</v>
+      </c>
+      <c r="H155" s="4">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J155" s="4">
+        <v>0.12675</v>
+      </c>
+      <c r="K155" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>3120014728</v>
       </c>
-      <c r="B156" s="4"/>
+      <c r="B156" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C156" s="4" t="s">
         <v>230</v>
       </c>
@@ -26680,17 +27937,29 @@
       <c r="F156" s="4">
         <v>37</v>
       </c>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
-      <c r="K156" s="4"/>
-    </row>
-    <row r="157" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G156" s="4">
+        <v>5</v>
+      </c>
+      <c r="H156" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J156" s="4">
+        <v>0.12778500000000001</v>
+      </c>
+      <c r="K156" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>3120014729</v>
       </c>
-      <c r="B157" s="4"/>
+      <c r="B157" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C157" s="4" t="s">
         <v>230</v>
       </c>
@@ -26703,17 +27972,29 @@
       <c r="F157" s="4">
         <v>63</v>
       </c>
-      <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
-      <c r="K157" s="4"/>
-    </row>
-    <row r="158" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G157" s="4">
+        <v>6</v>
+      </c>
+      <c r="H157" s="4">
+        <v>0.151</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J157" s="4">
+        <v>0.12881999999999999</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>3120014729</v>
       </c>
-      <c r="B158" s="4"/>
+      <c r="B158" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C158" s="4" t="s">
         <v>230</v>
       </c>
@@ -26726,17 +28007,29 @@
       <c r="F158" s="4">
         <v>37</v>
       </c>
-      <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
-      <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
-      <c r="K158" s="4"/>
-    </row>
-    <row r="159" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G158" s="4">
+        <v>7</v>
+      </c>
+      <c r="H158" s="4">
+        <v>0.152</v>
+      </c>
+      <c r="I158" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J158" s="4">
+        <v>0.129855</v>
+      </c>
+      <c r="K158" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>3120014730</v>
       </c>
-      <c r="B159" s="4"/>
+      <c r="B159" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C159" s="4" t="s">
         <v>230</v>
       </c>
@@ -26749,17 +28042,29 @@
       <c r="F159" s="4">
         <v>63</v>
       </c>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-      <c r="I159" s="4"/>
-      <c r="J159" s="4"/>
-      <c r="K159" s="4"/>
-    </row>
-    <row r="160" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G159" s="4">
+        <v>8</v>
+      </c>
+      <c r="H159" s="4">
+        <v>0.153</v>
+      </c>
+      <c r="I159" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J159" s="4">
+        <v>0.13089000000000001</v>
+      </c>
+      <c r="K159" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>3120014730</v>
       </c>
-      <c r="B160" s="4"/>
+      <c r="B160" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C160" s="4" t="s">
         <v>230</v>
       </c>
@@ -26772,17 +28077,29 @@
       <c r="F160" s="4">
         <v>37</v>
       </c>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
-      <c r="K160" s="4"/>
-    </row>
-    <row r="161" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G160" s="4">
+        <v>9</v>
+      </c>
+      <c r="H160" s="4">
+        <v>0.154</v>
+      </c>
+      <c r="I160" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J160" s="4">
+        <v>0.13192499999999999</v>
+      </c>
+      <c r="K160" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>3120014731</v>
       </c>
-      <c r="B161" s="4"/>
+      <c r="B161" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C161" s="4" t="s">
         <v>234</v>
       </c>
@@ -26795,17 +28112,29 @@
       <c r="F161" s="4">
         <v>63</v>
       </c>
-      <c r="G161" s="4"/>
-      <c r="H161" s="4"/>
-      <c r="I161" s="4"/>
-      <c r="J161" s="4"/>
-      <c r="K161" s="4"/>
-    </row>
-    <row r="162" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G161" s="4">
+        <v>10</v>
+      </c>
+      <c r="H161" s="4">
+        <v>0.155</v>
+      </c>
+      <c r="I161" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J161" s="4">
+        <v>0.13295999999999999</v>
+      </c>
+      <c r="K161" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>3120014731</v>
       </c>
-      <c r="B162" s="4"/>
+      <c r="B162" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C162" s="4" t="s">
         <v>234</v>
       </c>
@@ -26818,17 +28147,29 @@
       <c r="F162" s="4">
         <v>37</v>
       </c>
-      <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
-      <c r="I162" s="4"/>
-      <c r="J162" s="4"/>
-      <c r="K162" s="4"/>
-    </row>
-    <row r="163" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G162" s="4">
+        <v>1</v>
+      </c>
+      <c r="H162" s="4">
+        <v>0.156</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J162" s="4">
+        <v>0.133995</v>
+      </c>
+      <c r="K162" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>3120014732</v>
       </c>
-      <c r="B163" s="4"/>
+      <c r="B163" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C163" s="4" t="s">
         <v>234</v>
       </c>
@@ -26841,17 +28182,29 @@
       <c r="F163" s="4">
         <v>63</v>
       </c>
-      <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
-      <c r="I163" s="4"/>
-      <c r="J163" s="4"/>
-      <c r="K163" s="4"/>
-    </row>
-    <row r="164" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G163" s="4">
+        <v>2</v>
+      </c>
+      <c r="H163" s="4">
+        <v>0.157</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J163" s="4">
+        <v>0.13503000000000001</v>
+      </c>
+      <c r="K163" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>3120014732</v>
       </c>
-      <c r="B164" s="4"/>
+      <c r="B164" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C164" s="4" t="s">
         <v>230</v>
       </c>
@@ -26864,17 +28217,29 @@
       <c r="F164" s="4">
         <v>37</v>
       </c>
-      <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
-      <c r="I164" s="4"/>
-      <c r="J164" s="4"/>
-      <c r="K164" s="4"/>
-    </row>
-    <row r="165" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G164" s="4">
+        <v>3</v>
+      </c>
+      <c r="H164" s="4">
+        <v>0.158</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J164" s="4">
+        <v>0.13606499999999999</v>
+      </c>
+      <c r="K164" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>3120014733</v>
       </c>
-      <c r="B165" s="4"/>
+      <c r="B165" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C165" s="4" t="s">
         <v>230</v>
       </c>
@@ -26887,17 +28252,29 @@
       <c r="F165" s="4">
         <v>63</v>
       </c>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
-      <c r="J165" s="4"/>
-      <c r="K165" s="4"/>
-    </row>
-    <row r="166" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G165" s="4">
+        <v>4</v>
+      </c>
+      <c r="H165" s="4">
+        <v>0.159</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J165" s="4">
+        <v>0.1371</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>3120014733</v>
       </c>
-      <c r="B166" s="4"/>
+      <c r="B166" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C166" s="4" t="s">
         <v>230</v>
       </c>
@@ -26910,17 +28287,29 @@
       <c r="F166" s="4">
         <v>37</v>
       </c>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
-      <c r="I166" s="4"/>
-      <c r="J166" s="4"/>
-      <c r="K166" s="4"/>
-    </row>
-    <row r="167" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G166" s="4">
+        <v>5</v>
+      </c>
+      <c r="H166" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="I166" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J166" s="4">
+        <v>0.13813500000000001</v>
+      </c>
+      <c r="K166" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>3120014734</v>
       </c>
-      <c r="B167" s="4"/>
+      <c r="B167" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C167" s="4" t="s">
         <v>234</v>
       </c>
@@ -26933,17 +28322,29 @@
       <c r="F167" s="4">
         <v>63</v>
       </c>
-      <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
-      <c r="I167" s="4"/>
-      <c r="J167" s="4"/>
-      <c r="K167" s="4"/>
-    </row>
-    <row r="168" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G167" s="4">
+        <v>6</v>
+      </c>
+      <c r="H167" s="4">
+        <v>0.161</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J167" s="4">
+        <v>0.13916999999999999</v>
+      </c>
+      <c r="K167" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>3120014734</v>
       </c>
-      <c r="B168" s="4"/>
+      <c r="B168" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C168" s="4" t="s">
         <v>234</v>
       </c>
@@ -26956,17 +28357,29 @@
       <c r="F168" s="4">
         <v>37</v>
       </c>
-      <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
-      <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
-      <c r="K168" s="4"/>
-    </row>
-    <row r="169" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G168" s="4">
+        <v>7</v>
+      </c>
+      <c r="H168" s="4">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J168" s="4">
+        <v>0.140205</v>
+      </c>
+      <c r="K168" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>3120014735</v>
       </c>
-      <c r="B169" s="4"/>
+      <c r="B169" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C169" s="4" t="s">
         <v>230</v>
       </c>
@@ -26979,17 +28392,29 @@
       <c r="F169" s="4">
         <v>63</v>
       </c>
-      <c r="G169" s="4"/>
-      <c r="H169" s="4"/>
-      <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
-      <c r="K169" s="4"/>
-    </row>
-    <row r="170" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G169" s="4">
+        <v>8</v>
+      </c>
+      <c r="H169" s="4">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J169" s="4">
+        <v>0.14124</v>
+      </c>
+      <c r="K169" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>3120014735</v>
       </c>
-      <c r="B170" s="4"/>
+      <c r="B170" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C170" s="4" t="s">
         <v>234</v>
       </c>
@@ -27002,17 +28427,29 @@
       <c r="F170" s="4">
         <v>37</v>
       </c>
-      <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
-      <c r="I170" s="4"/>
-      <c r="J170" s="4"/>
-      <c r="K170" s="4"/>
-    </row>
-    <row r="171" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G170" s="4">
+        <v>9</v>
+      </c>
+      <c r="H170" s="4">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J170" s="4">
+        <v>0.14227500000000001</v>
+      </c>
+      <c r="K170" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>3120014737</v>
       </c>
-      <c r="B171" s="4"/>
+      <c r="B171" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C171" s="4" t="s">
         <v>170</v>
       </c>
@@ -27025,17 +28462,29 @@
       <c r="F171" s="4">
         <v>100</v>
       </c>
-      <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
-      <c r="I171" s="4"/>
-      <c r="J171" s="4"/>
-      <c r="K171" s="4"/>
-    </row>
-    <row r="172" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G171" s="4">
+        <v>10</v>
+      </c>
+      <c r="H171" s="4">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J171" s="4">
+        <v>0.14330999999999999</v>
+      </c>
+      <c r="K171" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>3120014738</v>
       </c>
-      <c r="B172" s="4"/>
+      <c r="B172" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C172" s="4" t="s">
         <v>170</v>
       </c>
@@ -27048,17 +28497,29 @@
       <c r="F172" s="4">
         <v>100</v>
       </c>
-      <c r="G172" s="4"/>
-      <c r="H172" s="4"/>
-      <c r="I172" s="4"/>
-      <c r="J172" s="4"/>
-      <c r="K172" s="4"/>
-    </row>
-    <row r="173" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G172" s="4">
+        <v>1</v>
+      </c>
+      <c r="H172" s="4">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J172" s="4">
+        <v>0.144345</v>
+      </c>
+      <c r="K172" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>3120014742</v>
       </c>
-      <c r="B173" s="4"/>
+      <c r="B173" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C173" s="4" t="s">
         <v>161</v>
       </c>
@@ -27071,17 +28532,29 @@
       <c r="F173" s="4">
         <v>100</v>
       </c>
-      <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
-      <c r="I173" s="4"/>
-      <c r="J173" s="4"/>
-      <c r="K173" s="4"/>
-    </row>
-    <row r="174" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G173" s="4">
+        <v>2</v>
+      </c>
+      <c r="H173" s="4">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J173" s="4">
+        <v>0.14538000000000001</v>
+      </c>
+      <c r="K173" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>3120014743</v>
       </c>
-      <c r="B174" s="4"/>
+      <c r="B174" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C174" s="4" t="s">
         <v>170</v>
       </c>
@@ -27094,17 +28567,29 @@
       <c r="F174" s="4">
         <v>100</v>
       </c>
-      <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="4"/>
-      <c r="J174" s="4"/>
-      <c r="K174" s="4"/>
-    </row>
-    <row r="175" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G174" s="4">
+        <v>3</v>
+      </c>
+      <c r="H174" s="4">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J174" s="4">
+        <v>0.14641499999999999</v>
+      </c>
+      <c r="K174" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>3120014744</v>
       </c>
-      <c r="B175" s="4"/>
+      <c r="B175" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C175" s="4" t="s">
         <v>170</v>
       </c>
@@ -27117,17 +28602,29 @@
       <c r="F175" s="4">
         <v>100</v>
       </c>
-      <c r="G175" s="4"/>
-      <c r="H175" s="4"/>
-      <c r="I175" s="4"/>
-      <c r="J175" s="4"/>
-      <c r="K175" s="4"/>
-    </row>
-    <row r="176" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G175" s="4">
+        <v>4</v>
+      </c>
+      <c r="H175" s="4">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J175" s="4">
+        <v>0.14745</v>
+      </c>
+      <c r="K175" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>3120014745</v>
       </c>
-      <c r="B176" s="4"/>
+      <c r="B176" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C176" s="4" t="s">
         <v>170</v>
       </c>
@@ -27140,17 +28637,29 @@
       <c r="F176" s="4">
         <v>100</v>
       </c>
-      <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
-      <c r="I176" s="4"/>
-      <c r="J176" s="4"/>
-      <c r="K176" s="4"/>
-    </row>
-    <row r="177" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G176" s="4">
+        <v>5</v>
+      </c>
+      <c r="H176" s="4">
+        <v>0.17</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J176" s="4">
+        <v>0.14848500000000001</v>
+      </c>
+      <c r="K176" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>3120014747</v>
       </c>
-      <c r="B177" s="4"/>
+      <c r="B177" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="C177" s="4" t="s">
         <v>235</v>
       </c>
@@ -27163,17 +28672,29 @@
       <c r="F177" s="4">
         <v>100</v>
       </c>
-      <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
-      <c r="I177" s="4"/>
-      <c r="J177" s="4"/>
-      <c r="K177" s="4"/>
-    </row>
-    <row r="178" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G177" s="4">
+        <v>6</v>
+      </c>
+      <c r="H177" s="4">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J177" s="4">
+        <v>0.14951999999999999</v>
+      </c>
+      <c r="K177" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>3120014748</v>
       </c>
-      <c r="B178" s="4"/>
+      <c r="B178" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="C178" s="4" t="s">
         <v>235</v>
       </c>
@@ -27186,17 +28707,29 @@
       <c r="F178" s="4">
         <v>100</v>
       </c>
-      <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
-      <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
-      <c r="K178" s="4"/>
-    </row>
-    <row r="179" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G178" s="4">
+        <v>7</v>
+      </c>
+      <c r="H178" s="4">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J178" s="4">
+        <v>0.15055499999999999</v>
+      </c>
+      <c r="K178" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>3120014754</v>
       </c>
-      <c r="B179" s="4"/>
+      <c r="B179" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C179" s="4" t="s">
         <v>230</v>
       </c>
@@ -27209,17 +28742,29 @@
       <c r="F179" s="4">
         <v>63</v>
       </c>
-      <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
-      <c r="I179" s="4"/>
-      <c r="J179" s="4"/>
-      <c r="K179" s="4"/>
-    </row>
-    <row r="180" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G179" s="4">
+        <v>8</v>
+      </c>
+      <c r="H179" s="4">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J179" s="4">
+        <v>0.15159</v>
+      </c>
+      <c r="K179" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>3120014754</v>
       </c>
-      <c r="B180" s="4"/>
+      <c r="B180" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C180" s="4" t="s">
         <v>234</v>
       </c>
@@ -27232,17 +28777,29 @@
       <c r="F180" s="4">
         <v>37</v>
       </c>
-      <c r="G180" s="4"/>
-      <c r="H180" s="4"/>
-      <c r="I180" s="4"/>
-      <c r="J180" s="4"/>
-      <c r="K180" s="4"/>
-    </row>
-    <row r="181" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G180" s="4">
+        <v>9</v>
+      </c>
+      <c r="H180" s="4">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J180" s="4">
+        <v>0.15262500000000001</v>
+      </c>
+      <c r="K180" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>3120014756</v>
       </c>
-      <c r="B181" s="4"/>
+      <c r="B181" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C181" s="4" t="s">
         <v>161</v>
       </c>
@@ -27255,17 +28812,29 @@
       <c r="F181" s="4">
         <v>100</v>
       </c>
-      <c r="G181" s="4"/>
-      <c r="H181" s="4"/>
-      <c r="I181" s="4"/>
-      <c r="J181" s="4"/>
-      <c r="K181" s="4"/>
-    </row>
-    <row r="182" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G181" s="4">
+        <v>10</v>
+      </c>
+      <c r="H181" s="4">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J181" s="4">
+        <v>0.15365999999999999</v>
+      </c>
+      <c r="K181" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>3120014757</v>
       </c>
-      <c r="B182" s="4"/>
+      <c r="B182" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C182" s="4" t="s">
         <v>170</v>
       </c>
@@ -27278,17 +28847,29 @@
       <c r="F182" s="4">
         <v>100</v>
       </c>
-      <c r="G182" s="4"/>
-      <c r="H182" s="4"/>
-      <c r="I182" s="4"/>
-      <c r="J182" s="4"/>
-      <c r="K182" s="4"/>
-    </row>
-    <row r="183" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G182" s="4">
+        <v>1</v>
+      </c>
+      <c r="H182" s="4">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J182" s="4">
+        <v>0.154695</v>
+      </c>
+      <c r="K182" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>3120014823</v>
       </c>
-      <c r="B183" s="4"/>
+      <c r="B183" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C183" s="4" t="s">
         <v>161</v>
       </c>
@@ -27301,17 +28882,29 @@
       <c r="F183" s="4">
         <v>100</v>
       </c>
-      <c r="G183" s="4"/>
-      <c r="H183" s="4"/>
-      <c r="I183" s="4"/>
-      <c r="J183" s="4"/>
-      <c r="K183" s="4"/>
-    </row>
-    <row r="184" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G183" s="4">
+        <v>2</v>
+      </c>
+      <c r="H183" s="4">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J183" s="4">
+        <v>0.15573000000000001</v>
+      </c>
+      <c r="K183" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>3120014824</v>
       </c>
-      <c r="B184" s="4"/>
+      <c r="B184" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C184" s="4" t="s">
         <v>170</v>
       </c>
@@ -27324,17 +28917,29 @@
       <c r="F184" s="4">
         <v>100</v>
       </c>
-      <c r="G184" s="4"/>
-      <c r="H184" s="4"/>
-      <c r="I184" s="4"/>
-      <c r="J184" s="4"/>
-      <c r="K184" s="4"/>
-    </row>
-    <row r="185" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G184" s="4">
+        <v>3</v>
+      </c>
+      <c r="H184" s="4">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J184" s="4">
+        <v>0.15676499999999999</v>
+      </c>
+      <c r="K184" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>3120014825</v>
       </c>
-      <c r="B185" s="4"/>
+      <c r="B185" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C185" s="4" t="s">
         <v>170</v>
       </c>
@@ -27347,17 +28952,29 @@
       <c r="F185" s="4">
         <v>100</v>
       </c>
-      <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
-      <c r="K185" s="4"/>
-    </row>
-    <row r="186" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G185" s="4">
+        <v>4</v>
+      </c>
+      <c r="H185" s="4">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J185" s="4">
+        <v>0.1578</v>
+      </c>
+      <c r="K185" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>3120014826</v>
       </c>
-      <c r="B186" s="4"/>
+      <c r="B186" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C186" s="4" t="s">
         <v>161</v>
       </c>
@@ -27370,17 +28987,29 @@
       <c r="F186" s="4">
         <v>100</v>
       </c>
-      <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-      <c r="I186" s="4"/>
-      <c r="J186" s="4"/>
-      <c r="K186" s="4"/>
-    </row>
-    <row r="187" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G186" s="4">
+        <v>5</v>
+      </c>
+      <c r="H186" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J186" s="4">
+        <v>0.158835</v>
+      </c>
+      <c r="K186" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>3120014827</v>
       </c>
-      <c r="B187" s="4"/>
+      <c r="B187" s="4" t="s">
+        <v>339</v>
+      </c>
       <c r="C187" s="4" t="s">
         <v>170</v>
       </c>
@@ -27393,17 +29022,29 @@
       <c r="F187" s="4">
         <v>100</v>
       </c>
-      <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
-      <c r="I187" s="4"/>
-      <c r="J187" s="4"/>
-      <c r="K187" s="4"/>
-    </row>
-    <row r="188" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G187" s="4">
+        <v>6</v>
+      </c>
+      <c r="H187" s="4">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J187" s="4">
+        <v>0.15987000000000001</v>
+      </c>
+      <c r="K187" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>3120015057</v>
       </c>
-      <c r="B188" s="4"/>
+      <c r="B188" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C188" s="4" t="s">
         <v>230</v>
       </c>
@@ -27416,17 +29057,29 @@
       <c r="F188" s="4">
         <v>63</v>
       </c>
-      <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
-      <c r="I188" s="4"/>
-      <c r="J188" s="4"/>
-      <c r="K188" s="4"/>
-    </row>
-    <row r="189" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G188" s="4">
+        <v>7</v>
+      </c>
+      <c r="H188" s="4">
+        <v>0.182</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J188" s="4">
+        <v>0.16090499999999999</v>
+      </c>
+      <c r="K188" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>3120015057</v>
       </c>
-      <c r="B189" s="4"/>
+      <c r="B189" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C189" s="4" t="s">
         <v>230</v>
       </c>
@@ -27439,17 +29092,29 @@
       <c r="F189" s="4">
         <v>37</v>
       </c>
-      <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
-      <c r="I189" s="4"/>
-      <c r="J189" s="4"/>
-      <c r="K189" s="4"/>
-    </row>
-    <row r="190" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G189" s="4">
+        <v>8</v>
+      </c>
+      <c r="H189" s="4">
+        <v>0.183</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J189" s="4">
+        <v>0.16194</v>
+      </c>
+      <c r="K189" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>3120015084</v>
       </c>
-      <c r="B190" s="4"/>
+      <c r="B190" s="4" t="s">
+        <v>337</v>
+      </c>
       <c r="C190" s="4" t="s">
         <v>236</v>
       </c>
@@ -27462,17 +29127,29 @@
       <c r="F190" s="4">
         <v>85</v>
       </c>
-      <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
-      <c r="I190" s="4"/>
-      <c r="J190" s="4"/>
-      <c r="K190" s="4"/>
-    </row>
-    <row r="191" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G190" s="4">
+        <v>9</v>
+      </c>
+      <c r="H190" s="4">
+        <v>0.184</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J190" s="4">
+        <v>0.16297500000000001</v>
+      </c>
+      <c r="K190" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>3120015084</v>
       </c>
-      <c r="B191" s="4"/>
+      <c r="B191" s="4" t="s">
+        <v>337</v>
+      </c>
       <c r="C191" s="4" t="s">
         <v>236</v>
       </c>
@@ -27485,17 +29162,29 @@
       <c r="F191" s="4">
         <v>15</v>
       </c>
-      <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
-      <c r="I191" s="4"/>
-      <c r="J191" s="4"/>
-      <c r="K191" s="4"/>
-    </row>
-    <row r="192" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G191" s="4">
+        <v>10</v>
+      </c>
+      <c r="H191" s="4">
+        <v>0.185</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J191" s="4">
+        <v>0.16400999999999999</v>
+      </c>
+      <c r="K191" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>3120015391</v>
       </c>
-      <c r="B192" s="4"/>
+      <c r="B192" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="C192" s="4" t="s">
         <v>235</v>
       </c>
@@ -27508,17 +29197,29 @@
       <c r="F192" s="4">
         <v>100</v>
       </c>
-      <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
-      <c r="I192" s="4"/>
-      <c r="J192" s="4"/>
-      <c r="K192" s="4"/>
-    </row>
-    <row r="193" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G192" s="4">
+        <v>1</v>
+      </c>
+      <c r="H192" s="4">
+        <v>0.186</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J192" s="4">
+        <v>0.165045</v>
+      </c>
+      <c r="K192" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>3120015392</v>
       </c>
-      <c r="B193" s="4"/>
+      <c r="B193" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="C193" s="4" t="s">
         <v>235</v>
       </c>
@@ -27531,17 +29232,29 @@
       <c r="F193" s="4">
         <v>100</v>
       </c>
-      <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
-      <c r="I193" s="4"/>
-      <c r="J193" s="4"/>
-      <c r="K193" s="4"/>
-    </row>
-    <row r="194" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G193" s="4">
+        <v>2</v>
+      </c>
+      <c r="H193" s="4">
+        <v>0.187</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J193" s="4">
+        <v>0.16608000000000001</v>
+      </c>
+      <c r="K193" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>3120015393</v>
       </c>
-      <c r="B194" s="4"/>
+      <c r="B194" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="C194" s="4" t="s">
         <v>235</v>
       </c>
@@ -27554,17 +29267,29 @@
       <c r="F194" s="4">
         <v>100</v>
       </c>
-      <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
-      <c r="I194" s="4"/>
-      <c r="J194" s="4"/>
-      <c r="K194" s="4"/>
-    </row>
-    <row r="195" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G194" s="4">
+        <v>3</v>
+      </c>
+      <c r="H194" s="4">
+        <v>0.188</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J194" s="4">
+        <v>0.16711500000000001</v>
+      </c>
+      <c r="K194" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>3120016298</v>
       </c>
-      <c r="B195" s="4"/>
+      <c r="B195" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="C195" s="4" t="s">
         <v>235</v>
       </c>
@@ -27577,17 +29302,29 @@
       <c r="F195" s="4">
         <v>100</v>
       </c>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-      <c r="I195" s="4"/>
-      <c r="J195" s="4"/>
-      <c r="K195" s="4"/>
-    </row>
-    <row r="196" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G195" s="4">
+        <v>4</v>
+      </c>
+      <c r="H195" s="4">
+        <v>0.189</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J195" s="4">
+        <v>0.16814999999999999</v>
+      </c>
+      <c r="K195" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>3120016450</v>
       </c>
-      <c r="B196" s="4"/>
+      <c r="B196" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="C196" s="4" t="s">
         <v>235</v>
       </c>
@@ -27600,13 +29337,23 @@
       <c r="F196" s="4">
         <v>100</v>
       </c>
-      <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
-      <c r="K196" s="4"/>
-    </row>
-    <row r="197" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G196" s="4">
+        <v>5</v>
+      </c>
+      <c r="H196" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J196" s="4">
+        <v>0.169185</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>3121010037</v>
       </c>
@@ -27623,17 +29370,29 @@
       <c r="F197" s="4">
         <v>100</v>
       </c>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
-      <c r="I197" s="4"/>
-      <c r="J197" s="4"/>
-      <c r="K197" s="4"/>
+      <c r="G197" s="4">
+        <v>6</v>
+      </c>
+      <c r="H197" s="4">
+        <v>0.191</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J197" s="4">
+        <v>0.17022000000000001</v>
+      </c>
+      <c r="K197" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="198" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>3121010038</v>
       </c>
-      <c r="B198" s="4"/>
+      <c r="B198" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C198" s="4" t="s">
         <v>229</v>
       </c>
@@ -27646,17 +29405,29 @@
       <c r="F198" s="4">
         <v>100</v>
       </c>
-      <c r="G198" s="4"/>
-      <c r="H198" s="4"/>
-      <c r="I198" s="4"/>
-      <c r="J198" s="4"/>
-      <c r="K198" s="4"/>
+      <c r="G198" s="4">
+        <v>7</v>
+      </c>
+      <c r="H198" s="4">
+        <v>0.192</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J198" s="4">
+        <v>0.17125499999999999</v>
+      </c>
+      <c r="K198" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="199" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>3121010039</v>
       </c>
-      <c r="B199" s="4"/>
+      <c r="B199" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="C199" s="4" t="s">
         <v>229</v>
       </c>
@@ -27669,17 +29440,29 @@
       <c r="F199" s="4">
         <v>100</v>
       </c>
-      <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
-      <c r="I199" s="4"/>
-      <c r="J199" s="4"/>
-      <c r="K199" s="4"/>
-    </row>
-    <row r="200" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G199" s="4">
+        <v>8</v>
+      </c>
+      <c r="H199" s="4">
+        <v>0.193</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J199" s="4">
+        <v>0.17229</v>
+      </c>
+      <c r="K199" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>3121010124</v>
       </c>
-      <c r="B200" s="4"/>
+      <c r="B200" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C200" s="4" t="s">
         <v>230</v>
       </c>
@@ -27692,17 +29475,29 @@
       <c r="F200" s="4">
         <v>63</v>
       </c>
-      <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
-      <c r="I200" s="4"/>
-      <c r="J200" s="4"/>
-      <c r="K200" s="4"/>
-    </row>
-    <row r="201" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G200" s="4">
+        <v>9</v>
+      </c>
+      <c r="H200" s="4">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J200" s="4">
+        <v>0.17332500000000001</v>
+      </c>
+      <c r="K200" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>3121010124</v>
       </c>
-      <c r="B201" s="4"/>
+      <c r="B201" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C201" s="4" t="s">
         <v>234</v>
       </c>
@@ -27715,17 +29510,29 @@
       <c r="F201" s="4">
         <v>37</v>
       </c>
-      <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
-      <c r="I201" s="4"/>
-      <c r="J201" s="4"/>
-      <c r="K201" s="4"/>
-    </row>
-    <row r="202" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G201" s="4">
+        <v>10</v>
+      </c>
+      <c r="H201" s="4">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J201" s="4">
+        <v>0.17435999999999999</v>
+      </c>
+      <c r="K201" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>3121010125</v>
       </c>
-      <c r="B202" s="4"/>
+      <c r="B202" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C202" s="4" t="s">
         <v>230</v>
       </c>
@@ -27738,17 +29545,29 @@
       <c r="F202" s="4">
         <v>63</v>
       </c>
-      <c r="G202" s="4"/>
-      <c r="H202" s="4"/>
-      <c r="I202" s="4"/>
-      <c r="J202" s="4"/>
-      <c r="K202" s="4"/>
-    </row>
-    <row r="203" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G202" s="4">
+        <v>1</v>
+      </c>
+      <c r="H202" s="4">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J202" s="4">
+        <v>0.175395</v>
+      </c>
+      <c r="K202" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>3121010125</v>
       </c>
-      <c r="B203" s="4"/>
+      <c r="B203" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C203" s="4" t="s">
         <v>230</v>
       </c>
@@ -27761,17 +29580,29 @@
       <c r="F203" s="4">
         <v>37</v>
       </c>
-      <c r="G203" s="4"/>
-      <c r="H203" s="4"/>
-      <c r="I203" s="4"/>
-      <c r="J203" s="4"/>
-      <c r="K203" s="4"/>
-    </row>
-    <row r="204" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G203" s="4">
+        <v>2</v>
+      </c>
+      <c r="H203" s="4">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J203" s="4">
+        <v>0.17643</v>
+      </c>
+      <c r="K203" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>3121010126</v>
       </c>
-      <c r="B204" s="4"/>
+      <c r="B204" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C204" s="4" t="s">
         <v>230</v>
       </c>
@@ -27784,17 +29615,29 @@
       <c r="F204" s="4">
         <v>63</v>
       </c>
-      <c r="G204" s="4"/>
-      <c r="H204" s="4"/>
-      <c r="I204" s="4"/>
-      <c r="J204" s="4"/>
-      <c r="K204" s="4"/>
-    </row>
-    <row r="205" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G204" s="4">
+        <v>3</v>
+      </c>
+      <c r="H204" s="4">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J204" s="4">
+        <v>0.17746500000000001</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>3121010126</v>
       </c>
-      <c r="B205" s="4"/>
+      <c r="B205" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C205" s="4" t="s">
         <v>230</v>
       </c>
@@ -27807,17 +29650,29 @@
       <c r="F205" s="4">
         <v>37</v>
       </c>
-      <c r="G205" s="4"/>
-      <c r="H205" s="4"/>
-      <c r="I205" s="4"/>
-      <c r="J205" s="4"/>
-      <c r="K205" s="4"/>
-    </row>
-    <row r="206" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G205" s="4">
+        <v>4</v>
+      </c>
+      <c r="H205" s="4">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J205" s="4">
+        <v>0.17849999999999999</v>
+      </c>
+      <c r="K205" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>3121010128</v>
       </c>
-      <c r="B206" s="4"/>
+      <c r="B206" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C206" s="4" t="s">
         <v>230</v>
       </c>
@@ -27830,17 +29685,29 @@
       <c r="F206" s="4">
         <v>63</v>
       </c>
-      <c r="G206" s="4"/>
-      <c r="H206" s="4"/>
-      <c r="I206" s="4"/>
-      <c r="J206" s="4"/>
-      <c r="K206" s="4"/>
-    </row>
-    <row r="207" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G206" s="4">
+        <v>5</v>
+      </c>
+      <c r="H206" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="I206" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J206" s="4">
+        <v>0.179535</v>
+      </c>
+      <c r="K206" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>3121010128</v>
       </c>
-      <c r="B207" s="4"/>
+      <c r="B207" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C207" s="4" t="s">
         <v>230</v>
       </c>
@@ -27853,17 +29720,29 @@
       <c r="F207" s="4">
         <v>37</v>
       </c>
-      <c r="G207" s="4"/>
-      <c r="H207" s="4"/>
-      <c r="I207" s="4"/>
-      <c r="J207" s="4"/>
-      <c r="K207" s="4"/>
-    </row>
-    <row r="208" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G207" s="4">
+        <v>6</v>
+      </c>
+      <c r="H207" s="4">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="I207" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J207" s="4">
+        <v>0.18057000000000001</v>
+      </c>
+      <c r="K207" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>3121010135</v>
       </c>
-      <c r="B208" s="4"/>
+      <c r="B208" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C208" s="4" t="s">
         <v>230</v>
       </c>
@@ -27876,17 +29755,29 @@
       <c r="F208" s="4">
         <v>63</v>
       </c>
-      <c r="G208" s="4"/>
-      <c r="H208" s="4"/>
-      <c r="I208" s="4"/>
-      <c r="J208" s="4"/>
-      <c r="K208" s="4"/>
-    </row>
-    <row r="209" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G208" s="4">
+        <v>7</v>
+      </c>
+      <c r="H208" s="4">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="I208" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J208" s="4">
+        <v>0.18160499999999999</v>
+      </c>
+      <c r="K208" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>3121010135</v>
       </c>
-      <c r="B209" s="4"/>
+      <c r="B209" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="C209" s="4" t="s">
         <v>230</v>
       </c>
@@ -27899,17 +29790,29 @@
       <c r="F209" s="4">
         <v>37</v>
       </c>
-      <c r="G209" s="4"/>
-      <c r="H209" s="4"/>
-      <c r="I209" s="4"/>
-      <c r="J209" s="4"/>
-      <c r="K209" s="4"/>
-    </row>
-    <row r="210" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G209" s="4">
+        <v>8</v>
+      </c>
+      <c r="H209" s="4">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="I209" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J209" s="4">
+        <v>0.18264</v>
+      </c>
+      <c r="K209" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>3121010283</v>
       </c>
-      <c r="B210" s="4"/>
+      <c r="B210" s="4" t="s">
+        <v>337</v>
+      </c>
       <c r="C210" s="4" t="s">
         <v>236</v>
       </c>
@@ -27922,17 +29825,29 @@
       <c r="F210" s="4">
         <v>85</v>
       </c>
-      <c r="G210" s="4"/>
-      <c r="H210" s="4"/>
-      <c r="I210" s="4"/>
-      <c r="J210" s="4"/>
-      <c r="K210" s="4"/>
-    </row>
-    <row r="211" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="G210" s="4">
+        <v>9</v>
+      </c>
+      <c r="H210" s="4">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="I210" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J210" s="4">
+        <v>0.183675</v>
+      </c>
+      <c r="K210" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>3121010283</v>
       </c>
-      <c r="B211" s="4"/>
+      <c r="B211" s="4" t="s">
+        <v>337</v>
+      </c>
       <c r="C211" s="4" t="s">
         <v>236</v>
       </c>
@@ -27945,14 +29860,33 @@
       <c r="F211" s="4">
         <v>15</v>
       </c>
-      <c r="G211" s="4"/>
-      <c r="H211" s="4"/>
-      <c r="I211" s="4"/>
-      <c r="J211" s="4"/>
-      <c r="K211" s="4"/>
+      <c r="G211" s="4">
+        <v>10</v>
+      </c>
+      <c r="H211" s="4">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I211" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="J211" s="4">
+        <v>0.18471000000000001</v>
+      </c>
+      <c r="K211" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B212" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K211" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:K211" xr:uid="{00000000-0009-0000-0000-000004000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="CU SN6"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="150" verticalDpi="150" r:id="rId1"/>
